--- a/doc/rtu_接口对照表.xlsx
+++ b/doc/rtu_接口对照表.xlsx
@@ -1038,22 +1038,22 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU→(RTU)</t>
+          <t xml:space="preserve">IDU→RTU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">preg_dealloc_mask[63:0]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="0">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU 侧没有对应输入：释放的所有权在 RTU（退休时按 old != dst）⇒ 可丢弃（先确认 IDU 不靠它做内部记账）</t>
+          <t xml:space="preserve">【改 RTU 侧：已于 2026-10-08 补口】⚠️ 极性：**位 = 1 表示这个号还被 store 引用着，不许回池**（名字里的 dealloc 读成"可以释放这些"正好反过来）。它是所有存活 SDIQ 表项的 src0 preg 的独热或（ct_idu_is_sdiq.sv:388-406）。**为什么必须接**：store 的"完成"不蕴含"数据已读"（lsu_st_da.sv:309）⇒ 更年轻的覆盖同一条 lreg 的指令退休时会把它还要读的号放回池子 ⇒ 重分配 ⇒ 静默错数。RTU 侧收下它是当**否决**用：释放先落第 5 态 RELEASE，掩码撤下才回 FREE。⚠️ 两个契约：① IDU 必须在冲刷那拍把它清零（不然号永久停在 RELEASE）；② 它只覆盖 SDIQ 的 src0（= store 数据），基址若在弹出后被重读则兜不住。⚠️ 交付的 IDU 里 SDIQ 表项的时钟 `src_mask_clk` 全仓无驱动 ⇒ 掩码恒 0，属"先决条件"（见下）。</t>
         </is>
       </c>
     </row>
@@ -1155,6 +1155,43 @@
       <c r="G32" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">⚠️ 交付的 IDU 里 **RAT 表项没接时钟**（ct_idu_dep_reg_src2_entry 的 preg 挂在 write_clk 上，全目录无驱动；例化也没连 forever_cpuclk）⇒ 改名表一个字写不进去。这是接它之前必须先修的先决条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">约束（非端口）</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU 内部</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">⚠️ **2026-10-08 新发现，同一类毛病**：SDIQ 里 `ct_idu_is_sdiq.sv:38-39` 的 `src_mask_clk` / `cnt_clk` 也**全仓无驱动**（该文件只在 :139/:376/:394 把它们当 always 的时钟用）。后果有两个：① 上面那根 `preg_dealloc_mask` 的寄存器永不翻转 ⇒ 恒 0；② SDIQ 自己的表项计数器 `sdiq_entry_cnt` 也不动 ⇒ 它的满/空判据是死的。⇒ 接线前必须补上（与 RAT 时钟一起修）</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1881,7 @@
       </c>
       <c r="C5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="0">
@@ -1866,7 +1903,7 @@
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="0">
@@ -1888,7 +1925,7 @@
       </c>
       <c r="C7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="0">
@@ -1927,7 +1964,7 @@
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">① RTU↔IDU 的"新增"全在 IDU 侧（派遣记录 39 根），且 `pc`/`chk` 连 C910 都没有，是真·新增；RTU 侧一根端口都不用加</t>
+          <t xml:space="preserve">① RTU↔IDU 的"新增"**绝大多数在 IDU 侧**（派遣记录 39 根），且 `pc`/`chk` 连 C910 都没有，是真·新增。⚠️ **2026-10-08 改口**：RTU 侧原本"一根端口都不用加"，现在要加 **1 根** —— `preg_dealloc_mask`（第 5 态 RELEASE 的否决口，理由见上）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="0">
@@ -1971,7 +2008,7 @@
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">③ 两个交付物都带了"我们没有的口"：IDU 的 `dealloc_mask`、LSU 的 `preg_expand` —— 它们都是 C910 那套**按 preg 广播**的残留，而我们按 iid 寻址 ⇒ 统一归到"暂无对应"，不接线</t>
+          <t xml:space="preserve">③ 两个交付物都带了"我们没有的口"：~~IDU 的 `dealloc_mask`~~、LSU 的 `preg_expand` —— ⚠️ **2026-10-08 修正**：这两者本不是一类，当时归错了。`dealloc_mask` 是**寿命**信息（"这个号还被 store 引用着"），与"按 iid 还是按 preg 寻址"正交 ⇒ **必须接**（已接）；剩下 LSU 的 `preg_expand` 才是真的"按 preg 广播的残留" ⇒ 它归"暂无对应"</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="0">

--- a/doc/rtu_接口对照表.xlsx
+++ b/doc/rtu_接口对照表.xlsx
@@ -459,7 +459,7 @@
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 派遣记录（13 根/路 × 3 路 = 39 根）—— 全部是 IDU 侧新增</t>
+          <t xml:space="preserve">## 派遣记录 —— ✅ 2026-10-08 已落地（IDU 侧加口 + 按车道录出，36 根）</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
@@ -471,7 +471,7 @@
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
@@ -491,24 +491,24 @@
       </c>
       <c r="E13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有）</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_vld</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 内部在 IS 派发级（ctrl_is_dis_inst*_vld），没往外引</t>
+          <t xml:space="preserve">✅ **已落地**。锚点 = `ct_idu_is_ctrl` 新加的 `ctrl_dp_dis_inst{k}_vld`（= `is_dis_inst{k}_vld &amp;&amp; !ctrl_is_dis_stall`）。⚠️ **不是** `ctrl_dp_dis_inst{k}_preg_vld` —— 那个还串了 `dst_vld`，只在该路**写寄存器**时有效；store/分支/跳转不写 rd 但都要建表项</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
@@ -518,34 +518,34 @@
       </c>
       <c r="C14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_pc[31:0]</t>
+          <t xml:space="preserve">disp*_pc[31:0] / disp*_chk[24:0]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×32</t>
+          <t xml:space="preserve">3×32 / 3×25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有）</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_pc / _chk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×32 / 3×25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 内部有（IFU 97 位包的 [63:32]）。⚠️ C910 也不送 pc（它靠 IU 里的 pcfifo）</t>
+          <t xml:space="preserve">✅ **已落地**。源 = `ct_idu_is_dp` 按车道录出的 `is_inst{k}_create_{pc,chk}`（派遣当拍的最终值，已含 pipedown2 的 mux）。pc 只取 [31:0]（内部 65 位是 {taken,npc,pc}）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="0">
@@ -555,34 +555,34 @@
       </c>
       <c r="C15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_chk[24:0]</t>
+          <t xml:space="preserve">disp*_{dst_lreg,rf_we,dst_preg,old_preg,src1_preg}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×25</t>
+          <t xml:space="preserve">3×(5+1+7+7+7)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（完全没有）</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_同名字段</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×(5+1+7+7+7)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">**IDU 完全没有这条路**：ifu2 的 chk 是独立旁路、不在 97 位包里 ⇒ 加输入口 + 随指令锁到派遣点</t>
+          <t xml:space="preserve">✅ **已落地**。IDU 是 6 位 preg、RTU 端口 7 位 ⇒ 高位补 0（PREG=64 档下本来就恒 0）。⚠️ **A6d 已在 IDU 侧补上**：`ct_idu_id_decd.sv:156` 是 `assign dst_reg = rd;`，**不写寄存器时并不清零**（store 的 rd 位是立即数）⇒ 已用 `{5{rf_we}} &amp; dst_reg` 掩过，否则 RTU 会按"要写 rd"分配编号而退休时又不写 ⇒ 编号静默泄漏。⚠️ **`src1_preg` 取 `data[48:43]` 不是 [48:42]** —— 那 7 位是 `{preg[5:0], wb_valid}`</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="0">
@@ -592,34 +592,34 @@
       </c>
       <c r="C16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_dst_lreg[4:0]</t>
+          <t xml:space="preserve">disp*_csr_addr / _op / _imm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×5</t>
+          <t xml:space="preserve">3×(12+3+5)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有）</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_csr_addr / _op / _imm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×(12+3+5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 id_decd 的 dst_reg；A6d：不写寄存器时必须给 0</t>
+          <t xml:space="preserve">✅ **已落地**。从 IS 级数据里的原始指令字切：[31:20] / [14:12] / [19:15]。A6c 天然满足（就是 funct3 原样）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="0">
@@ -629,54 +629,54 @@
       </c>
       <c r="C17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_rf_we</t>
+          <t xml:space="preserve">disp*_flags[6:0]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有）</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_flags[6:0]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 dst_vld；A6b：要与写回级同源（difftest 连 ena 都比）</t>
+          <t xml:space="preserve">✅ **已落地**。位序 = `RTU_FLG_*`：{is_jalr,is_jal,is_mret,is_csr,intmask,is_store,is_branch}。jal/jalr/csr/mret 从原始指令字现解；is_store/is_branch 用 IS 级的 `IS_STORE`/`IS_BJU`。⚠️ **`intmask` 恒 0**：RTU 侧全仓 grep 只有 `RTU_FLG_INTMASK` 的定义与端口注释、**零消费点**，所以没花力气解它（将来 RTU 真要用时这里要按"这条能不能被中断打断"重解）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">暂无对应</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU→RTU</t>
+          <t xml:space="preserve">IDU→(RTU)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_dst_preg[6:0]</t>
+          <t xml:space="preserve">disp*_sq_id[2:0]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">3×3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有）</t>
+          <t xml:space="preserve">—（故意没加）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="0">
@@ -686,7 +686,7 @@
       </c>
       <c r="G18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 ir_inst*_dst_preg（就是它从 RTU 拿到的号，6 位）</t>
+          <t xml:space="preserve">⚠️ **这次没做**，是有意的：IDU 的 SDIQ（4 项）**不是** LSU 的 SQ（6 项），两者不是同一个队列；且 LSU 那侧是按 **iid 广播**找表项的（`rtu_yy_xx_commit*`），根本不需要槽号。⇒ 等跟 LSU 确认"到底要不要这根线"之后再定，先不造一根语义不清的</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="C19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_old_preg[6:0]</t>
+          <t xml:space="preserve">disp*_vld</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="0">
@@ -723,7 +723,7 @@
       </c>
       <c r="G19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 RAT 读口 rt_dp_inst*_rel_preg</t>
+          <t xml:space="preserve">IDU 内部在 IS 派发级（ctrl_is_dis_inst*_vld），没往外引</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="C20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_src1_preg[6:0]</t>
+          <t xml:space="preserve">disp*_pc[31:0]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">3×32</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="0">
@@ -760,7 +760,7 @@
       </c>
       <c r="G20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 rt_dp_inst*_src1_data；**只有 CSR 指令有意义**</t>
+          <t xml:space="preserve">IDU 内部有（IFU 97 位包的 [63:32]）。⚠️ C910 也不送 pc（它靠 IU 里的 pcfifo）</t>
         </is>
       </c>
     </row>
@@ -777,27 +777,27 @@
       </c>
       <c r="C21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_csr_addr / _op / _imm</t>
+          <t xml:space="preserve">disp*_chk[24:0]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">12/3/5</t>
+          <t xml:space="preserve">3×25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有）</t>
+          <t xml:space="preserve">（输入口已有；IS 级内部已有）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有（译码）；A6c：csr_op 要 **funct3 原样**（001/010/011 与 101/110/111）</t>
+          <t xml:space="preserve">⚠️ **2026-10-08 改口（commit cbcbd18 "idu chk"）**：原来写的"IDU 完全没有这条路、要加输入口 + 随指令锁存"**已作废** —— 同事把两件事都做了：① 顶层加了输入 `ifu_idu_if_inst0/1/2_chk[24:0]`；② chk 随指令走完 IF→ID→IR→IS 全程（`ct_idu_is_pipe_entry` 的 `entry_chk` 存进 IS 队列，`ct_idu_is_dp.sv` 的 `is_inst{k}_read_chk` 在读出侧现成）。⇒ **只剩"把 IS 读出侧的 chk 引到顶层给 RTU"这一步**，不需要再动流水线。⚠️ 但注意 BIQ 只有 2 个 create 口（`is_biq_create0/1_chk`），RTU 要的是**3 路**（任意一路都可能是分支）⇒ 派遣点的取法要按 3 路重取，不能直接抄 BIQ 那两路</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="C22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_flags[6:0]</t>
+          <t xml:space="preserve">disp*_dst_lreg[4:0]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">3×5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="0">
@@ -834,7 +834,7 @@
       </c>
       <c r="G22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部散在 inst_type[4:0] / ir_decd；要按 RTU_FLG_* 打包{is_jalr,is_jal,is_mret,is_csr,intmask,is_store,is_branch}</t>
+          <t xml:space="preserve">内部有 id_decd 的 dst_reg；A6d：不写寄存器时必须给 0</t>
         </is>
       </c>
     </row>
@@ -851,17 +851,17 @@
       </c>
       <c r="C23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_sq_id[2:0]</t>
+          <t xml:space="preserve">disp*_rf_we</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×3</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有类似的）</t>
+          <t xml:space="preserve">—（缺，内部有）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="0">
@@ -871,34 +871,34 @@
       </c>
       <c r="G23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 内部有 SDIQ 条目号，但那是**发射级**发给 LSU 的；RTU 要的是**派遣当拍**的槽号</t>
+          <t xml:space="preserve">内部有 dst_vld；A6b：要与写回级同源（difftest 连 ena 都比）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">约束（非端口）</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 侧</t>
+          <t xml:space="preserve">IDU→RTU</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">disp*_dst_preg[6:0]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">—（缺，内部有）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="0">
@@ -908,83 +908,108 @@
       </c>
       <c r="G24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">A7：**一拍最多一条 CSR**（RTU 的 CSR 是单槽）；组内第二条要连同后面的指令截到下一拍</t>
+          <t xml:space="preserve">内部有 ir_inst*_dst_preg（就是它从 RTU 拿到的号，6 位）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 冲刷 与 映射恢复</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">IDU→RTU</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">disp*_old_preg[6:0]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×7</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—（缺，内部有）</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">内部有 RAT 读口 rt_dp_inst*_rel_preg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→IDU</t>
+          <t xml:space="preserve">IDU→RTU</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_ren_flush (+ rtu_backend_flush)</t>
+          <t xml:space="preserve">disp*_src1_preg[6:0]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_yy_xx_flush</t>
+          <t xml:space="preserve">—（缺，内部有）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">两边都是 T+1 那拍。⚠️ **别接 rtu_core_redirect**（T 拍，早一拍）</t>
+          <t xml:space="preserve">内部有 rt_dp_inst*_src1_data；**只有 CSR 指令有意义**</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→(IDU)</t>
+          <t xml:space="preserve">IDU→RTU</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_ren_recover_vld</t>
+          <t xml:space="preserve">disp*_csr_addr / _op / _imm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12/3/5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">—（缺，内部有）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="0">
@@ -994,44 +1019,44 @@
       </c>
       <c r="G27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 的写使能就是 flush 本身（同拍组合写 RAT），没有单独的 vld 口 ⇒ 可省</t>
+          <t xml:space="preserve">内部有（译码）；A6c：csr_op 要 **funct3 原样**（001/010/011 与 101/110/111）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·需适配</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→IDU</t>
+          <t xml:space="preserve">IDU→RTU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_ren_recover_map[223:0]</t>
+          <t xml:space="preserve">disp*_flags[6:0]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">224</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_idu_rt_recover_preg[191:0]</t>
+          <t xml:space="preserve">—（缺，内部有）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">192</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">两边都是"32 个 lreg 的架构映射"，但**布局不同**（32×7 vs 32×6 每槽切位） ⇒ 适配层逐槽重排，不是切低位</t>
+          <t xml:space="preserve">内部散在 inst_type[4:0] / ir_decd；要按 RTU_FLG_* 打包{is_jalr,is_jal,is_mret,is_csr,intmask,is_store,is_branch}</t>
         </is>
       </c>
     </row>
@@ -1048,44 +1073,44 @@
       </c>
       <c r="C29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">preg_dealloc_mask[63:0]</t>
+          <t xml:space="preserve">disp*_sq_id[2:0]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">3×3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_rtu_pst_preg_dealloc_mask[63:0]</t>
+          <t xml:space="preserve">—（缺，内部有类似的）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">【改 RTU 侧：已于 2026-10-08 补口】⚠️ 极性：**位 = 1 表示这个号还被 store 引用着，不许回池**（名字里的 dealloc 读成"可以释放这些"正好反过来）。它是所有存活 SDIQ 表项的 src0 preg 的独热或（ct_idu_is_sdiq.sv:388-406）。**为什么必须接**：store 的"完成"不蕴含"数据已读"（lsu_st_da.sv:309）⇒ 更年轻的覆盖同一条 lreg 的指令退休时会把它还要读的号放回池子 ⇒ 重分配 ⇒ 静默错数。RTU 侧收下它是当**否决**用：释放先落第 5 态 RELEASE，掩码撤下才回 FREE。⚠️ 两个契约：① IDU 必须在冲刷那拍把它清零（不然号永久停在 RELEASE）；② 它只覆盖 SDIQ 的 src0（= store 数据），基址若在弹出后被重读则兜不住。⚠️ 交付的 IDU 里 SDIQ 表项的时钟 `src_mask_clk` 全仓无驱动 ⇒ 掩码恒 0，属"先决条件"（见下）。</t>
+          <t xml:space="preserve">IDU 内部有 SDIQ 条目号，但那是**发射级**发给 LSU 的；RTU 要的是**派遣当拍**的槽号</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">(适配层)</t>
+          <t xml:space="preserve">IDU 侧</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">复位极性</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="0">
@@ -1095,7 +1120,7 @@
       </c>
       <c r="E30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">cpurst_b 低有效</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="0">
@@ -1105,14 +1130,14 @@
       </c>
       <c r="G30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 是 cpurst_b 低有效异步 / RTU 是 cpu_rst 高有效 ⇒ 适配层反相</t>
+          <t xml:space="preserve">A7：**一拍最多一条 CSR**（RTU 的 CSR 是单槽）；组内第二条要连同后面的指令截到下一拍</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 先决条件（不是端口，但接之前必须先修）</t>
+          <t xml:space="preserve">## IDU 顶层端口表变更（2026-10-08, commit cbcbd18 "idu chk"） —— 与 RTU 无关，但影响接线与冒烟台</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="0">
@@ -1124,17 +1149,17 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">约束（非端口）</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 内部</t>
+          <t xml:space="preserve">IFU→IDU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">—（ifu2 不需要改）</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="0">
@@ -1144,52 +1169,409 @@
       </c>
       <c r="E32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">ifu_idu_if_inst0/1/2_chk[24:0]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">⚠️ 交付的 IDU 里 **RAT 表项没接时钟**（ct_idu_dep_reg_src2_entry 的 preg 挂在 write_clk 上，全目录无驱动；例化也没连 forever_cpuclk）⇒ 改名表一个字写不进去。这是接它之前必须先修的先决条件</t>
+          <t xml:space="preserve">IDU **新增的输入口**。ifu2 侧本来就有这三根旁路输出（`rv32ifu2_top.v:204/207/210` 的 `idu_inst0/1/2_chk[24:0]`）⇒ 直接接。⚠️ 旧文档说"现核里 chk 只走了 0 路、ifu2 的 inst1/inst2_chk 在 mycpu.v:417/420 悬空"—— 接 C910 IDU 时这三根要全部接上</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">已有·直接接</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU→IFU</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">idu_accept_num[1:0]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">⚠️ **IDU 顶层把 `idu_ifu_inst0/1/2_ready` 三个输出删了，换成这一根**（同一次提交）。编码 `{inst2_ready|inst0_ready, inst2_ready}`（`ct_idu_top.sv:180`），取值只有 **{0,1,3}** —— 2 不可达（因为 `inst0_ready==inst1_ready` 恒相等，见 `ct_idu_id_ctrl.sv:36-38`）。语义 = **本拍从 IFU 收下几条（程序序前缀）**。✅ **ifu2 早就有这个口**（`rv32ifu2_top.v:212` "同拍消费的前缀条数"）⇒ 这次改动是**把 IDU 对齐到 ifu2**，不是新增负担</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">需新增</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU→(BIQ/BU)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">idu_biq_chk[24:0]</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">同一次提交新增的输出，把 chk 送到 BIQ（分支执行路径）。与 RTU 无关；记在这里是因为它是 `disp*_chk` 之外的第二个 chk 出口，别接混</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr" s="0">
+      <c r="B35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TB 侧</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">⚠️ **冒烟台已过时**：`tb/unit/tb_idu_c910.sv` 的端口连接是 `scripts/gen_idu_smoke_tb.py` 从 `ct_idu_top.sv` 端口表生成的，现在它还连着已删掉的 `idu_ifu_inst0/1/2_ready`，且缺 chk 三根 / `idu_accept_num` / `idu_biq_chk`。实测 `python3 scripts/gen_idu_smoke_tb.py --check` 报"需要重新生成" ⇒ **`make idu-unit` 现在会 elaborate 失败**，跑之前先重跑生成器</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">## 冲刷 与 映射恢复</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">已有·直接接</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">RTU→IDU</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_ren_flush (+ rtu_backend_flush)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_yy_xx_flush</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">两边都是 T+1 那拍。⚠️ **别接 rtu_core_redirect**（T 拍，早一拍）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">暂无对应</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">RTU→(IDU)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_ren_recover_vld</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU 的写使能就是 flush 本身（同拍组合写 RAT），没有单独的 vld 口 ⇒ 可省</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">已有·需适配</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">RTU→IDU</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_ren_recover_map[223:0]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">224</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_idu_rt_recover_preg[191:0]</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">192</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">两边都是"32 个 lreg 的架构映射"，但**布局不同**（32×7 vs 32×6 每槽切位） ⇒ 适配层逐槽重排，不是切低位</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">需新增</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU→RTU</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">preg_dealloc_mask[63:0]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">64</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">idu_rtu_pst_preg_dealloc_mask[63:0]</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">64</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">【改 RTU 侧：已于 2026-10-08 补口】⚠️ 极性：**位 = 1 表示这个号还被 store 引用着，不许回池**（名字里的 dealloc 读成"可以释放这些"正好反过来）。它是所有存活 SDIQ 表项的 src0 preg 的独热或（ct_idu_is_sdiq.sv:388-406）。**为什么必须接**：store 的"完成"不蕴含"数据已读"（lsu_st_da.sv:309）⇒ 更年轻的覆盖同一条 lreg 的指令退休时会把它还要读的号放回池子 ⇒ 重分配 ⇒ 静默错数。RTU 侧收下它是当**否决**用：释放先落第 5 态 RELEASE，掩码撤下才回 FREE。⚠️ 两个契约：① IDU 必须在冲刷那拍把它清零（不然号永久停在 RELEASE）；② 它只覆盖 SDIQ 的 src0（= store 数据），基址若在弹出后被重读则兜不住。⚠️ 交付的 IDU 里 SDIQ 表项的时钟 `src_mask_clk` 全仓无驱动 ⇒ 掩码恒 0，属"先决条件"（见下）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">需新增</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">(适配层)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">复位极性</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">cpurst_b 低有效</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU 是 cpurst_b 低有效异步 / RTU 是 cpu_rst 高有效 ⇒ 适配层反相</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">## 先决条件（不是端口，但接之前必须先修）</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">约束（非端口）</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">IDU 内部</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr" s="0">
+      <c r="C43" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">✅ **2026-10-08 已修，而且病因比原来记的多三条**。改名表要能用，**四处都得对**：① 表项时钟 `dep_clk`/`write_clk` 全仓无驱动（C910 工厂版的 gated clk cell 被剥掉了）；② `reg_write_en_arr[0:31]` **全文件没有任何赋值**（32 位总线算出来了没接过去）⇒ 写使能悬空 Z；③ 数组宽度错位：表项口是 `x_read_data[12:0]`/`x_create_data[10:0]`（C910 打包格式），wrapper 只声明成 **7 位** ⇒ 读侧截断、写侧错位。实测指纹：**给号 33 → 存进去变 8 → 读回来变 16**（每步错位 2 位）；④ `rt_reset_updt_preg`（x_l→p_l 复位映射）**零消费** ⇒ 上电后所有逻辑寄存器指向 p0。⚠️ **①②③ 已修并验证**（`make idu-unit` 的定向判据：某次派遣的 `old_preg` 必须变成 RTU 给的号）；**④ 还没修**，不修整核跑起来必错。详见 doc/DELIVERY_FIXES_2026-10-08.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">约束（非端口）</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU 内部</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">⚠️ **2026-10-08 新发现，同一类毛病**：SDIQ 里 `ct_idu_is_sdiq.sv:38-39` 的 `src_mask_clk` / `cnt_clk` 也**全仓无驱动**（该文件只在 :139/:376/:394 把它们当 always 的时钟用）。后果有两个：① 上面那根 `preg_dealloc_mask` 的寄存器永不翻转 ⇒ 恒 0；② SDIQ 自己的表项计数器 `sdiq_entry_cnt` 也不动 ⇒ 它的满/空判据是死的。⇒ 接线前必须补上（与 RAT 时钟一起修）</t>
         </is>
@@ -1449,7 +1831,7 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 提交 / 冲刷（RTU → LSU）</t>
+          <t xml:space="preserve">## 访存异常（LSU → RTU）—— 2026-10-08 新增，commit 3e605a0 "expt"</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
@@ -1461,133 +1843,133 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→LSU</t>
+          <t xml:space="preserve">LSU→RTU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_backend_flush</t>
+          <t xml:space="preserve">expt_vld / expt_iid[6:0] / expt_cause[4:0] / expt_tval[31:0]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 / 7 / 5 / 32</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_yy_xx_flush</t>
+          <t xml:space="preserve">lsu_rtu_wb_pipe3_expt_vld / _expt_addr[31:0]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1 / 32</t>
         </is>
       </c>
       <c r="G9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">都是 T+1 单拍脉冲</t>
+          <t xml:space="preserve">**load 侧异常**（新加的两根）。语义 = **地址非对齐**：`ld_ag_expt = !ld_ag_align`（`lsu_ld_ag.sv:286-297`，按 `{inst_size, addr[2:0]}` 判：BYTE 任意 / HALF 需 `addr[0]=0` / WORD 需 `addr[1:0]=00`），随流水 AG→DC→DA→WB 打到底，**与 `lsu_rtu_wb_pipe3_cmplt` 同拍、同 iid**。⇒ 映射：`expt_iid` = 同拍 `lsu_rtu_wb_pipe3_iid`（**原样，不许重编码**）；`expt_cause` = **5'd4**（`EXC_LOAD_MISALIGNED`，defines.vh:301）；`expt_tval` = `_expt_addr`（= `ld_da_addr`）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→LSU</t>
+          <t xml:space="preserve">LSU→RTU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_yy_xx_commit0/1/2  +  _iid</t>
+          <t xml:space="preserve">expt_vld / expt_iid[6:0] / expt_cause[4:0] / expt_tval[31:0]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3 + 21</t>
+          <t xml:space="preserve">1 / 7 / 5 / 32</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_yy_xx_commit0/1/2  +  _iid</t>
+          <t xml:space="preserve">lsu_rtu_wb_pipe4_expt_vld / _expt_addr[31:0]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3 + 21</t>
+          <t xml:space="preserve">1 / 32</t>
         </is>
       </c>
       <c r="G10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">**RTU 侧已加**（2026-10-08，照 C910 `ct_rtu_rob_rt.v:2723-2731`）：退休窗口 3 条 iid 广播 + **真的提交了**的脉冲（陷阱那条不发、被中断 squash 的不发）。两边都是寄存器输出、**成对锁存** —— 消费方必须同一个边沿成对采样</t>
+          <t xml:space="preserve">**store 侧异常**（同上）。`st_ag_expt = !st_ag_align`（`lsu_st_ag.sv:142-153`）。⇒ 映射：iid 取同拍 `lsu_rtu_wb_pipe4_iid`；cause = **5'd6**（`EXC_STORE_MISALIGNED`，defines.vh:303）；tval = `_expt_addr`（= `st_da_addr0`）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→LSU</t>
+          <t xml:space="preserve">适配层</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_lsu_async_flush</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_lsu_async_flush</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">**RTU 侧已加**（2026-10-08），当前**恒 0**：C910 里它是**调试请求**的异步冲刷（`ct_rtu_retire.v:2005` 的 `async_flush = dbgreq_ack_jdbreq`），本核没有 debug 模块。LSU 拿它清 WMB/SQ（lsu_sq.sv:527、lsu_wmb_ce.sv:62）；将来接 debug 时接到这里即可</t>
+          <t xml:space="preserve">🔴 **同拍两源必须比 iid 取最旧**。RTU 的异常口是**单路**（D9 的"全局单表项、最旧者胜"，`RTU_expt.v` 用 `RTU_iid_cmp` 跟手里的比），而 LSU 现在有**两个**源（load pipe3 / store pipe4）且两条流水独立、可以同拍都报。RTU 只能跟**已经收下的**比年龄 —— 所以**丢哪一条是适配层决定的**。若丢的是年长那条：RTU 手里只有年轻的，年长的那条**按正常流程退休走掉、异常永久丢失**（它不会被重取 —— 冲刷只冲比 trap 那条更年轻的）。用 `RTU_iid_cmp` 同款模比较。另一条路是把 RTU 的异常口加宽到 2 路（改 RTU 侧，动 §6.1 的 D9）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→(LSU)</t>
+          <t xml:space="preserve">LSU 侧</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_store_vld0/1/2</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="0">
@@ -1602,29 +1984,29 @@
       </c>
       <c r="G12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">我们 RTU §6.2 的 store 提交口；LSU 侧没有对应输入 ⇒ 若走"iid 广播"那套就不需要它</t>
+          <t xml:space="preserve">✅ **报异常时 LSU 会压掉访存**，口径自洽、不用 RTU 兜底：`st_da_rb_create_vld_unmask ... &amp;&amp; !st_da_expt`（不发总线写，`lsu_st_da.sv:293`）、`st_da_idu_secd_vld ... &amp;&amp; !st_da_expt`（不发第二拍，:332）、`ld_da_data_vld ... &amp;&amp; !ld_da_expt`（不写回，`lsu_ld_da.sv:521`）。配上 RTU 侧 `RTU_commit.v:294` 的 `commit_vld` 已经 `&amp; ~trap_hit`（陷阱那条**不发提交广播**）⇒ 非对齐 store **不会落内存**。两头正好对上</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→(LSU)</t>
+          <t xml:space="preserve">适配层</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_store_sq_id0/1/2[2:0]</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×3</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="0">
@@ -1639,71 +2021,71 @@
       </c>
       <c r="G13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">同上</t>
+          <t xml:space="preserve">🔴 **`expt_vld` 必须与同口的 `cmplt` 相与之后再送进 RTU**（iid/tval 也按那一拍取）。这不是保险，是必须 —— 两根的相位现在**不保证一致**：`lsu_ld_wb.sv:165-175` 那段新加的 `always` **缺 begin/end**，于是 `ld_wb_expt` / `ld_wb_expt_addr` 变成 `ld_wb_pre_expt_vld` / `ld_da_wb_expt_addr` 的**无条件一拍延迟**（只在 `if (!cpurst_b)` 和 `else if (ld_wb_pre_inst_vld)` 各自的第一句上有条件），而导出的 cmplt `lsu_rtu_wb_pipe3_cmplt = ld_wb_inst_vld` 是**有门控**的（:152-162，置位要 `ld_wb_pre_inst_vld`、冲刷那拍清零）⇒ **会出现 expt_vld=1 而 cmplt=0 的拍**，而那一拍的 `lsu_rtu_wb_pipe3_iid` 是**残留值**。真会碰上的两种情形：① 冲刷那拍（cmplt 被清、expt 不被清）；② `ld_da_wb_cmplt_req = ld_da_inst_vld &amp;&amp; !ld_da_secd`（`lsu_ld_da.sv:515`）而 `ld_da_wb_expt_vld = ld_da_expt`（:516）是**裸**的 —— `ld_da_expt` 只在复位与 `ld_dc_da_inst_vld` 时更新（:268/:292），**没有冲刷清零**，`ld_da_inst_vld` 却有 ⇒ 两者脱节。⚠️ 后果是**静默**的（不报 x/z）：拿裸 expt_vld 去报，会按错误 iid 报异常，RTU 收进单表项一直挂到那条 iid 退休 ⇒ 冤枉一条无辜指令陷入、或静默掐掉它的退休；只有 difftest 能抓。⇒ 建议同时请同事补上那段 begin/end —— **store 侧 `lsu_st_wb.sv:59-74` 写法是对的**（begin/end + 用 `st_wb_pre_inst_vld` 门控），照着改即可</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">暂无对应</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LSU→RTU</t>
+          <t xml:space="preserve">LSU→(RTU)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">sq_rdy0/1/2  (RTU 已声明)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（LSU 侧要产生）</t>
+          <t xml:space="preserve">lsu_rtu_async_expt_vld / _addr[31:0]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 / 32</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">【改 LSU 侧：产生这三根】RTU §6.1 已有这三个输入（"这条 store 的数据就绪了吗"），现在 mycpu.v 恒接 1</t>
+          <t xml:space="preserve">⚠️ **这两根现在只是 `lsu_top` 的内部信号**（`lsu_top.sv:685-686`），**没引到顶层** ⇒ RTU 拿不到"总线错误"这类异常。源在 `lsu_ld_wb.sv:264`（`ld_wb_data_vld &amp;&amp; ld_wb_bus_err`）。要不要引出来由 RTU↔LSU 定；现在归"暂无对应"，接线时要**显式确认**是"不需要"还是"漏了"</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LSU→RTU</t>
+          <t xml:space="preserve">IDU+LSU 口径</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">sq_stall  (RTU 已声明)</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（LSU 侧要产生）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="0">
@@ -1713,14 +2095,14 @@
       </c>
       <c r="G15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">【改 LSU 侧：产生这一根】存储队列满/下游忙 ⇒ 压退休宽度；现在恒接 0</t>
+          <t xml:space="preserve">❓ **非对齐到底走 trap 还是走硬件拆分**，两边还都留着通路：LSU 一边报 `expt` 并压掉访存，一边仍保留 `idu_lsu_{ld,st}_unalign_2nd` → `ld_ag_secd` / `st_ag_secd` 的**拆两次访存**机制（`lsu_ld_ag.sv:219`、`lsu_st_ag.sv`）。两者不能并存：**走 trap ⇒ IDU 不该再发 `unalign_2nd`；走拆分 ⇒ 就不该报 `expt`**。接 RTU 之前要跟 IDU/LSU 两位定死（RTU 只按"收到 expt 就用 cause 4/6 陷入"设计）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 约束（不是线，但接之前要知道）</t>
+          <t xml:space="preserve">## 提交 / 冲刷（RTU → LSU）</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="0">
@@ -1732,37 +2114,345 @@
     <row r="17">
       <c r="A17" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">已有·直接接</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">RTU→LSU</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_backend_flush</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_yy_xx_flush</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">都是 T+1 单拍脉冲</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">已有·直接接</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">RTU→LSU</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_yy_xx_commit0/1/2  +  _iid</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3 + 21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_yy_xx_commit0/1/2  +  _iid</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3 + 21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">**RTU 侧已加**（2026-10-08，照 C910 `ct_rtu_rob_rt.v:2723-2731`）：退休窗口 3 条 iid 广播 + **真的提交了**的脉冲（陷阱那条不发、被中断 squash 的不发）。两边都是寄存器输出、**成对锁存** —— 消费方必须同一个边沿成对采样</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">已有·直接接</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">RTU→LSU</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_lsu_async_flush</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_lsu_async_flush</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">**RTU 侧已加**（2026-10-08），当前**恒 0**：C910 里它是**调试请求**的异步冲刷（`ct_rtu_retire.v:2005` 的 `async_flush = dbgreq_ack_jdbreq`），本核没有 debug 模块。LSU 拿它清 WMB/SQ（lsu_sq.sv:527、lsu_wmb_ce.sv:62）；将来接 debug 时接到这里即可</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">暂无对应</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">RTU→(LSU)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_store_vld0/1/2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">我们 RTU §6.2 的 store 提交口；LSU 侧没有对应输入 ⇒ 若走"iid 广播"那套就不需要它</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">暂无对应</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">RTU→(LSU)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_store_sq_id0/1/2[2:0]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">需新增</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">LSU→RTU</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">sq_rdy0/1/2  (RTU 已声明)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—（LSU 侧要产生）</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">【改 LSU 侧：产生这三根】RTU §6.1 已有这三个输入（"这条 store 的数据就绪了吗"），现在 mycpu.v 恒接 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">需新增</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">LSU→RTU</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">sq_stall  (RTU 已声明)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—（LSU 侧要产生）</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">【改 LSU 侧：产生这一根】存储队列满/下游忙 ⇒ 压退休宽度；现在恒接 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">## 约束（不是线，但接之前要知道）</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr" s="0">
+      <c r="B25" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">RTU→LSU</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr" s="0">
+      <c r="C25" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">(rtu_yy_xx_commit*_iid)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr" s="0">
+      <c r="D25" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr" s="0">
+      <c r="E25" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">(LSU 内部表项里存的 iid)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr" s="0">
+      <c r="F25" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr" s="0">
+      <c r="G25" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">⚠️ 广播出去的 iid 必须与 LSU 表项里存的**是同一个号**（那个号追到源头就是 RTU 在派遣那拍发的 `rtu_disp_iid*`）⇒ **不许在适配层重编码、也不许偏一拍**，否则"段不匹配"的后果是静默的：store 永远等不到提交、或提前提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">约束（非端口）</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU+LSU 队列深度</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">disp*_sq_id[2:0]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SQ_ENTRY=6 / SDIQ_ENTRY=4 / LSIQ_ENTRY=8</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-10-08 核过的实际档位（`lsu_top.sv:3-5`）：`SQ_ENTRY = 6` ⇒ 槽号 0..5 正好 3 位，**与 RTU 的 `disp*_sq_id[2:0]` 严丝合缝**；`SDIQ_ENTRY = 4`（对 IDU 的 `idu_lsu_st_sdiq_entry[3:0]`）；`LSIQ_ENTRY = 8`（对 IDU 的 `idu_lsu_ld/st_lch_entry[7:0]`）。⚠️ **旧文档正文里写的 `LSIQ_ENTRY = 12` 已过期** —— 2026-10-08 的 commit 165dfd5 "位宽对齐 64 preg / 8 LSIQ" 已把它改成 8。RTU 只用 `sq_id`，与 LSIQ 深度无关</t>
         </is>
       </c>
     </row>
@@ -1837,7 +2527,7 @@
       </c>
       <c r="C3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="0">
@@ -1859,12 +2549,12 @@
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
@@ -1881,7 +2571,7 @@
       </c>
       <c r="C5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="0">
@@ -1903,12 +2593,12 @@
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
@@ -1925,12 +2615,12 @@
       </c>
       <c r="C7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -1964,7 +2654,7 @@
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">① RTU↔IDU 的"新增"**绝大多数在 IDU 侧**（派遣记录 39 根），且 `pc`/`chk` 连 C910 都没有，是真·新增。⚠️ **2026-10-08 改口**：RTU 侧原本"一根端口都不用加"，现在要加 **1 根** —— `preg_dealloc_mask`（第 5 态 RELEASE 的否决口，理由见上）</t>
+          <t xml:space="preserve">① **派遣记录 ✅ 已落地**（2026-10-08）：`ct_idu_top` 加了 **36 根**（3 路 × 12 字段），数据从 `ct_idu_is_dp` 按车道录出、vld 从 `ct_idu_is_ctrl` 引出。`disp*_sq_id` **有意没加**（IDU 的 SDIQ 不是 LSU 的 SQ，且 LSU 按 iid 广播找表项）—— 等跟 LSU 确认。⚠️ RTU 侧要加的仍是 **1 根**：`preg_dealloc_mask`</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="0">
@@ -1986,7 +2676,7 @@
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">② RTU↔LSU 的四项 RTU 侧改动**已于 2026-10-08 落地**（commit 广播口 / async_flush 占位 / store 重放输入 + 第 5 类冲刷源），剩 LSU 侧的 `sq_rdy*`/`sq_stall` 两根要它产生</t>
+          <t xml:space="preserve">② RTU↔LSU 的四项 RTU 侧改动**已于 2026-10-08 落地**（commit 广播口 / async_flush 占位 / store 重放输入 + 第 5 类冲刷源），剩 LSU 侧的 `sq_rdy*`/`sq_stall` 两根要它产生。⚠️ **同日晚些（commit 3e605a0）LSU 又加了 4 根访存异常线**（load/store 各一对），RTU 侧**不用改口**（走现成的 `expt_*` 收集口），但适配层多一条"两源取最旧"的硬约束</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
@@ -2030,7 +2720,7 @@
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">④ **接线前先修的两个先决条件 + 一个口径**：IDU 的 RAT 表项时钟、SDIQ 的 `src_mask_clk`/`cnt_clk`（都全仓无驱动）；以及**非对齐走 trap 还是走硬件拆分**（IDU/LSU 两位要定死，见 RTU↔LSU 表末）。⚠️ 另外 `tb/unit/tb_idu_c910.sv` 已随 IDU 端口表变更而过时，`make idu-unit` 现在会 elaborate 失败</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
@@ -2047,20 +2737,64 @@
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">引用</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="0">
+      <c r="B14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">详细论证：doc/idu_rtu_接口待办.txt（IDU 侧）、doc/rtu_plan_zh.md §6（契约）、doc/rtu_preg_size_config_zh.md（位数配置）</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr" s="0">
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">本次对齐的代码基线</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2026-10-08 拉取 origin/miniRV 至 commit 3e605a0 ("expt")。IDU = `mySoC/idu_c910/rtl/ct_idu_top.sv`，LSU = `mySoC/lsu/rtl/lsu_top.sv`，RTU = `mySoC/rtu/rtl/RTU.v` —— 三份端口表都逐条核过</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/doc/rtu_接口对照表.xlsx
+++ b/doc/rtu_接口对照表.xlsx
@@ -1831,7 +1831,7 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 访存异常（LSU → RTU）—— 2026-10-08 新增，commit 3e605a0 "expt"</t>
+          <t xml:space="preserve">## 访存异常（LSU → RTU）—— 2026-10-08 新增；2026-10-10 改成三路平行</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">expt_vld / expt_iid[6:0] / expt_cause[4:0] / expt_tval[31:0]</t>
+          <t xml:space="preserve">expt_ld_vld / expt_ld_iid[6:0] / expt_ld_cause[4:0] / expt_ld_tval[31:0]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="0">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">**load 侧异常**（新加的两根）。语义 = **地址非对齐**：`ld_ag_expt = !ld_ag_align`（`lsu_ld_ag.sv:286-297`，按 `{inst_size, addr[2:0]}` 判：BYTE 任意 / HALF 需 `addr[0]=0` / WORD 需 `addr[1:0]=00`），随流水 AG→DC→DA→WB 打到底，**与 `lsu_rtu_wb_pipe3_cmplt` 同拍、同 iid**。⇒ 映射：`expt_iid` = 同拍 `lsu_rtu_wb_pipe3_iid`（**原样，不许重编码**）；`expt_cause` = **5'd4**（`EXC_LOAD_MISALIGNED`，defines.vh:301）；`expt_tval` = `_expt_addr`（= `ld_da_addr`）</t>
+          <t xml:space="preserve">**load 侧异常**（新加的两根）。语义 = **地址非对齐**：`ld_ag_expt = !ld_ag_align`（`lsu_ld_ag.sv:286-297`，按 `{inst_size, addr[2:0]}` 判：BYTE 任意 / HALF 需 `addr[0]=0` / WORD 需 `addr[1:0]=00`），随流水 AG→DC→DA→WB 打到底，**与 `lsu_rtu_wb_pipe3_cmplt` 同拍、同 iid**。⇒ 映射：`expt_ld_iid` = 同拍 `lsu_rtu_wb_pipe3_iid`（**原样，不许重编码**）；`expt_ld_cause` = **5'd4**（`EXC_LOAD_MISALIGNED`，defines.vh:301）；`expt_ld_tval` = `_expt_addr`（= `ld_da_addr`）</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">expt_vld / expt_iid[6:0] / expt_cause[4:0] / expt_tval[31:0]</t>
+          <t xml:space="preserve">expt_st_vld / expt_st_iid[6:0] / expt_st_cause[4:0] / expt_st_tval[31:0]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="0">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="G10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">**store 侧异常**（同上）。`st_ag_expt = !st_ag_align`（`lsu_st_ag.sv:142-153`）。⇒ 映射：iid 取同拍 `lsu_rtu_wb_pipe4_iid`；cause = **5'd6**（`EXC_STORE_MISALIGNED`，defines.vh:303）；tval = `_expt_addr`（= `st_da_addr0`）</t>
+          <t xml:space="preserve">**store 侧异常**（同上）。`st_ag_expt = !st_ag_align`（`lsu_st_ag.sv:142-153`）。⇒ 映射：`expt_st_iid` 取同拍 `lsu_rtu_wb_pipe4_iid`；`expt_st_cause` = **5'd6**（`EXC_STORE_MISALIGNED`，defines.vh:303）；`expt_st_tval` = `_expt_addr`（= `st_da_addr0`）</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">🔴 **同拍两源必须比 iid 取最旧**。RTU 的异常口是**单路**（D9 的"全局单表项、最旧者胜"，`RTU_expt.v` 用 `RTU_iid_cmp` 跟手里的比），而 LSU 现在有**两个**源（load pipe3 / store pipe4）且两条流水独立、可以同拍都报。RTU 只能跟**已经收下的**比年龄 —— 所以**丢哪一条是适配层决定的**。若丢的是年长那条：RTU 手里只有年轻的，年长的那条**按正常流程退休走掉、异常永久丢失**（它不会被重取 —— 冲刷只冲比 trap 那条更年轻的）。用 `RTU_iid_cmp` 同款模比较。另一条路是把 RTU 的异常口加宽到 2 路（改 RTU 侧，动 §6.1 的 D9）</t>
+          <t xml:space="preserve">✅ **2026-10-10 已落地：适配层不再仲裁，三路平行送进 RTU**。原来的做法是「两源取最旧 + 再与其它源取最旧」，两个 `RTU_iid_cmp` 都在适配层 —— **那是个补不回来的窟窿**：load 与 store 是两条独立流水、可以同拍都报，上游只能送一条；若送的是年轻那条，年长那条的异常信息当场丢失、且**以后不会再报**（它已离开流水），而它比 trap 那条老 ⇒ **不在冲刷范围内** ⇒ 带着「无异常」的表项正常退休，异常**永久丢失**。RTU 内部那级（保持项「更老才覆盖」）只救得了**跨拍**冲突。⇒ 现在 RTU 的异常口是**三路**（`expt_iu_*` / `expt_ld_*` / `expt_st_*`），与 C910 的 `iu_rtu_pipe0 / pipe3 / pipe4_expt_*` 一一对应，锦标赛在 `RTU_expt` 里做（`cmp(iu,ld) → w1`、`cmp(w1,st) → w2`、`cmp(w2,held) → take`）。适配层只留「完成门控 + cause 编码」两件跨界必需的事。⚠️ 这正是本表原来写的「另一条路」（那时说的是加宽到 2 路），2026-10-10 按 3 路做了</t>
         </is>
       </c>
     </row>

--- a/doc/rtu_接口对照表.xlsx
+++ b/doc/rtu_接口对照表.xlsx
@@ -151,7 +151,7 @@
     <row r="3">
       <c r="A3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·需适配</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="0">
@@ -161,12 +161,12 @@
       </c>
       <c r="C3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ren_preg_req[1:0]</t>
+          <t xml:space="preserve">ren_preg_req[2:0]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="0">
@@ -181,7 +181,7 @@
       </c>
       <c r="G3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 发三路独立请求 vld；适配层数个数编成"程序序前缀"2 位。⚠️ 语义是"请求 = 当拍取走"(门房, 2026-10-07)</t>
+          <t xml:space="preserve">**逐路直传**（bit k = 车道 k 本拍取走号）。⚠️ 语义是"请求 = 当拍取走"（门房, 2026-10-07）。⚠️ **2026-10-12 改**：原来是 `[1:0]` 的"程序序前缀长度"、由适配层拿三路 vld **求和**编出来 —— 那个"求和 = 前缀"的假设不成立（`alloc_vld{k}` 是每条车道各自判的，车道 0 写 x0 时它是 0 而车道 2 照样可以是 1），会**漏号 + 可能重发**；改成逐路向量后那三根恒常量的 `ren_preg_req_lreg*` 一并删掉（x0 的排除 IDU 侧已经做了）。见 `a910_difftest_zh.md` §6.5</t>
         </is>
       </c>
     </row>
@@ -193,39 +193,39 @@
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">(适配层)</t>
+          <t xml:space="preserve">RTU→IDU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ren_preg_req_lreg0/1/2[4:0]</t>
+          <t xml:space="preserve">rtu_preg_alloc0/1/2[6:0]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×5</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（填常量）</t>
+          <t xml:space="preserve">rtu_idu_alloc_preg0/1/2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 没有"请求者的 dst lreg"输出；适配层填**非零常量**即可（IDU 的请求本身已排除 x0）</t>
+          <t xml:space="preserve">位宽 7→6：PREG=64 档下最高位恒 0 ⇒ 切 [5:0] 即可</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·需适配</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="0">
@@ -235,120 +235,120 @@
       </c>
       <c r="C5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_preg_alloc0/1/2[6:0]</t>
+          <t xml:space="preserve">rtu_preg_alloc_vld0/1/2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_idu_alloc_preg0/1/2</t>
+          <t xml:space="preserve">rtu_idu_alloc_preg0/1/2_vld</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×6</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">位宽 7→6：PREG=64 档下最高位恒 0 ⇒ 切 [5:0] 即可</t>
+          <t xml:space="preserve">同拍许可；为 0 时 IDU 必须停 IR 级（组合环已于 2026-10-07 断掉）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">暂无对应</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→IDU</t>
+          <t xml:space="preserve">RTU→(IDU)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_preg_alloc_vld0/1/2</t>
+          <t xml:space="preserve">rtu_preg_free_cnt[1:0]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_idu_alloc_preg0/1/2_vld</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">同拍许可；为 0 时 IDU 必须停 IR 级（组合环已于 2026-10-07 断掉）</t>
+          <t xml:space="preserve">IDU 不用它（按逐路 vld 自己停）；留作观察口</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">## iid 回执 与 停派遣</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→(IDU)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">rtu_preg_free_cnt[1:0]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">IDU 不用它（按逐路 vld 自己停）；留作观察口</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## iid 回执 与 停派遣</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">RTU→IDU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_disp_iid0/1/2[6:0]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_idu_rob_inst0/1/2_iid</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">位宽/相位完全对齐（两边都是"create 指针寄存器 + 组合"）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
@@ -358,34 +358,34 @@
       </c>
       <c r="C9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_disp_iid0/1/2[6:0]</t>
+          <t xml:space="preserve">rtu_disp_vld0/1/2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_idu_rob_inst0/1/2_iid</t>
+          <t xml:space="preserve">—（无此输入口）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">位宽/相位完全对齐（两边都是"create 指针寄存器 + 组合"）</t>
+          <t xml:space="preserve">IDU 没有"派遣被接受"的口；有 disp_stall 保证不越界即可。要用就得给 IDU 加口</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
@@ -395,83 +395,83 @@
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_disp_vld0/1/2</t>
+          <t xml:space="preserve">rtu_disp_stall</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（无此输入口）</t>
+          <t xml:space="preserve">rtu_idu_rob_full</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 没有"派遣被接受"的口；有 disp_stall 保证不越界即可。要用就得给 IDU 加口</t>
+          <t xml:space="preserve">两边都是"只依赖寄存器"的停派遣（C910 的 rob_full 也是寄存器）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">## 派遣记录 —— ✅ 2026-10-08 已落地（IDU 侧加口 + 按车道录出，36 根）</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→IDU</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">rtu_disp_stall</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">rtu_idu_rob_full</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">两边都是"只依赖寄存器"的停派遣（C910 的 rob_full 也是寄存器）</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 派遣记录 —— ✅ 2026-10-08 已落地（IDU 侧加口 + 按车道录出，36 根）</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">IDU→RTU</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">disp*_vld</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">idu_rtu_disp{k}_vld</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">✅ **已落地**。锚点 = `ct_idu_is_ctrl` 新加的 `ctrl_dp_dis_inst{k}_vld`（= `is_dis_inst{k}_vld &amp;&amp; !ctrl_is_dis_stall`）。⚠️ **不是** `ctrl_dp_dis_inst{k}_preg_vld` —— 那个还串了 `dst_vld`，只在该路**写寄存器**时有效；store/分支/跳转不写 rd 但都要建表项</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·需适配</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="0">
@@ -481,34 +481,34 @@
       </c>
       <c r="C13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_vld</t>
+          <t xml:space="preserve">disp*_pc[31:0] / disp*_chk[24:0]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">3×32 / 3×25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_rtu_disp{k}_vld</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_pc / _chk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">3×32 / 3×25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">✅ **已落地**。锚点 = `ct_idu_is_ctrl` 新加的 `ctrl_dp_dis_inst{k}_vld`（= `is_dis_inst{k}_vld &amp;&amp; !ctrl_is_dis_stall`）。⚠️ **不是** `ctrl_dp_dis_inst{k}_preg_vld` —— 那个还串了 `dst_vld`，只在该路**写寄存器**时有效；store/分支/跳转不写 rd 但都要建表项</t>
+          <t xml:space="preserve">✅ **已落地**。源 = `ct_idu_is_dp` 按车道录出的 `is_inst{k}_create_{pc,chk}`（派遣当拍的最终值，已含 pipedown2 的 mux）。pc 只取 [31:0]（内部 65 位是 {taken,npc,pc}）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
@@ -518,34 +518,34 @@
       </c>
       <c r="C14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_pc[31:0] / disp*_chk[24:0]</t>
+          <t xml:space="preserve">disp*_{dst_lreg,rf_we,dst_preg,old_preg,src1_preg}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×32 / 3×25</t>
+          <t xml:space="preserve">3×(5+1+7+7+7)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_rtu_disp{k}_pc / _chk</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_同名字段</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×32 / 3×25</t>
+          <t xml:space="preserve">3×(5+1+7+7+7)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">✅ **已落地**。源 = `ct_idu_is_dp` 按车道录出的 `is_inst{k}_create_{pc,chk}`（派遣当拍的最终值，已含 pipedown2 的 mux）。pc 只取 [31:0]（内部 65 位是 {taken,npc,pc}）</t>
+          <t xml:space="preserve">✅ **已落地**。IDU 是 6 位 preg、RTU 端口 7 位 ⇒ 高位补 0（PREG=64 档下本来就恒 0）。⚠️ **A6d 已在 IDU 侧补上**：`ct_idu_id_decd.sv:156` 是 `assign dst_reg = rd;`，**不写寄存器时并不清零**（store 的 rd 位是立即数）⇒ 已用 `{5{rf_we}} &amp; dst_reg` 掩过，否则 RTU 会按"要写 rd"分配编号而退休时又不写 ⇒ 编号静默泄漏。⚠️ **`src1_preg` 取 `data[48:43]` 不是 [48:42]** —— 那 7 位是 `{preg[5:0], wb_valid}`</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·需适配</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="0">
@@ -555,27 +555,27 @@
       </c>
       <c r="C15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_{dst_lreg,rf_we,dst_preg,old_preg,src1_preg}</t>
+          <t xml:space="preserve">disp*_csr_addr / _op / _imm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×(5+1+7+7+7)</t>
+          <t xml:space="preserve">3×(12+3+5)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_rtu_disp{k}_同名字段</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_csr_addr / _op / _imm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×(5+1+7+7+7)</t>
+          <t xml:space="preserve">3×(12+3+5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">✅ **已落地**。IDU 是 6 位 preg、RTU 端口 7 位 ⇒ 高位补 0（PREG=64 档下本来就恒 0）。⚠️ **A6d 已在 IDU 侧补上**：`ct_idu_id_decd.sv:156` 是 `assign dst_reg = rd;`，**不写寄存器时并不清零**（store 的 rd 位是立即数）⇒ 已用 `{5{rf_we}} &amp; dst_reg` 掩过，否则 RTU 会按"要写 rd"分配编号而退休时又不写 ⇒ 编号静默泄漏。⚠️ **`src1_preg` 取 `data[48:43]` 不是 [48:42]** —— 那 7 位是 `{preg[5:0], wb_valid}`</t>
+          <t xml:space="preserve">✅ **已落地**。从 IS 级数据里的原始指令字切：[31:20] / [14:12] / [19:15]。A6c 天然满足（就是 funct3 原样）</t>
         </is>
       </c>
     </row>
@@ -592,91 +592,91 @@
       </c>
       <c r="C16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_csr_addr / _op / _imm</t>
+          <t xml:space="preserve">disp*_flags[6:0]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×(12+3+5)</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_rtu_disp{k}_csr_addr / _op / _imm</t>
+          <t xml:space="preserve">idu_rtu_disp{k}_flags[6:0]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×(12+3+5)</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">✅ **已落地**。从 IS 级数据里的原始指令字切：[31:20] / [14:12] / [19:15]。A6c 天然满足（就是 funct3 原样）</t>
+          <t xml:space="preserve">✅ **已落地**。位序 = `RTU_FLG_*`：{is_jalr,is_jal,is_mret,is_csr,intmask,is_store,is_branch}。jal/jalr/csr/mret 从原始指令字现解；is_store/is_branch 用 IS 级的 `IS_STORE`/`IS_BJU`。⚠️ **`intmask` 恒 0**：RTU 侧全仓 grep 只有 `RTU_FLG_INTMASK` 的定义与端口注释、**零消费点**，所以没花力气解它（将来 RTU 真要用时这里要按"这条能不能被中断打断"重解）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">暂无对应</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU→RTU</t>
+          <t xml:space="preserve">IDU→(RTU)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_flags[6:0]</t>
+          <t xml:space="preserve">disp*_sq_id[2:0]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">3×3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_rtu_disp{k}_flags[6:0]</t>
+          <t xml:space="preserve">—（故意没加）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">✅ **已落地**。位序 = `RTU_FLG_*`：{is_jalr,is_jal,is_mret,is_csr,intmask,is_store,is_branch}。jal/jalr/csr/mret 从原始指令字现解；is_store/is_branch 用 IS 级的 `IS_STORE`/`IS_BJU`。⚠️ **`intmask` 恒 0**：RTU 侧全仓 grep 只有 `RTU_FLG_INTMASK` 的定义与端口注释、**零消费点**，所以没花力气解它（将来 RTU 真要用时这里要按"这条能不能被中断打断"重解）</t>
+          <t xml:space="preserve">⚠️ **这次没做**，是有意的：IDU 的 SDIQ（4 项）**不是** LSU 的 SQ（6 项），两者不是同一个队列；且 LSU 那侧是按 **iid 广播**找表项的（`rtu_yy_xx_commit*`），根本不需要槽号。⇒ 等跟 LSU 确认"到底要不要这根线"之后再定，先不造一根语义不清的</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU→(RTU)</t>
+          <t xml:space="preserve">IDU→RTU</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_sq_id[2:0]</t>
+          <t xml:space="preserve">disp*_vld</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×3</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（故意没加）</t>
+          <t xml:space="preserve">—（缺，内部有）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="0">
@@ -686,7 +686,7 @@
       </c>
       <c r="G18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">⚠️ **这次没做**，是有意的：IDU 的 SDIQ（4 项）**不是** LSU 的 SQ（6 项），两者不是同一个队列；且 LSU 那侧是按 **iid 广播**找表项的（`rtu_yy_xx_commit*`），根本不需要槽号。⇒ 等跟 LSU 确认"到底要不要这根线"之后再定，先不造一根语义不清的</t>
+          <t xml:space="preserve">IDU 内部在 IS 派发级（ctrl_is_dis_inst*_vld），没往外引</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="C19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_vld</t>
+          <t xml:space="preserve">disp*_pc[31:0]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">3×32</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="0">
@@ -723,7 +723,7 @@
       </c>
       <c r="G19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 内部在 IS 派发级（ctrl_is_dis_inst*_vld），没往外引</t>
+          <t xml:space="preserve">IDU 内部有（IFU 97 位包的 [63:32]）。⚠️ C910 也不送 pc（它靠 IU 里的 pcfifo）</t>
         </is>
       </c>
     </row>
@@ -740,27 +740,27 @@
       </c>
       <c r="C20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_pc[31:0]</t>
+          <t xml:space="preserve">disp*_chk[24:0]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×32</t>
+          <t xml:space="preserve">3×25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有）</t>
+          <t xml:space="preserve">（输入口已有；IS 级内部已有）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">3×25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 内部有（IFU 97 位包的 [63:32]）。⚠️ C910 也不送 pc（它靠 IU 里的 pcfifo）</t>
+          <t xml:space="preserve">⚠️ **2026-10-08 改口（commit cbcbd18 "idu chk"）**：原来写的"IDU 完全没有这条路、要加输入口 + 随指令锁存"**已作废** —— 同事把两件事都做了：① 顶层加了输入 `ifu_idu_if_inst0/1/2_chk[24:0]`；② chk 随指令走完 IF→ID→IR→IS 全程（`ct_idu_is_pipe_entry` 的 `entry_chk` 存进 IS 队列，`ct_idu_is_dp.sv` 的 `is_inst{k}_read_chk` 在读出侧现成）。⇒ **只剩"把 IS 读出侧的 chk 引到顶层给 RTU"这一步**，不需要再动流水线。⚠️ 但注意 BIQ 只有 2 个 create 口（`is_biq_create0/1_chk`），RTU 要的是**3 路**（任意一路都可能是分支）⇒ 派遣点的取法要按 3 路重取，不能直接抄 BIQ 那两路</t>
         </is>
       </c>
     </row>
@@ -777,27 +777,27 @@
       </c>
       <c r="C21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_chk[24:0]</t>
+          <t xml:space="preserve">disp*_dst_lreg[4:0]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×25</t>
+          <t xml:space="preserve">3×5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">（输入口已有；IS 级内部已有）</t>
+          <t xml:space="preserve">—（缺，内部有）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×25</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">⚠️ **2026-10-08 改口（commit cbcbd18 "idu chk"）**：原来写的"IDU 完全没有这条路、要加输入口 + 随指令锁存"**已作废** —— 同事把两件事都做了：① 顶层加了输入 `ifu_idu_if_inst0/1/2_chk[24:0]`；② chk 随指令走完 IF→ID→IR→IS 全程（`ct_idu_is_pipe_entry` 的 `entry_chk` 存进 IS 队列，`ct_idu_is_dp.sv` 的 `is_inst{k}_read_chk` 在读出侧现成）。⇒ **只剩"把 IS 读出侧的 chk 引到顶层给 RTU"这一步**，不需要再动流水线。⚠️ 但注意 BIQ 只有 2 个 create 口（`is_biq_create0/1_chk`），RTU 要的是**3 路**（任意一路都可能是分支）⇒ 派遣点的取法要按 3 路重取，不能直接抄 BIQ 那两路</t>
+          <t xml:space="preserve">内部有 id_decd 的 dst_reg；A6d：不写寄存器时必须给 0</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="C22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_dst_lreg[4:0]</t>
+          <t xml:space="preserve">disp*_rf_we</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×5</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="0">
@@ -834,7 +834,7 @@
       </c>
       <c r="G22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 id_decd 的 dst_reg；A6d：不写寄存器时必须给 0</t>
+          <t xml:space="preserve">内部有 dst_vld；A6b：要与写回级同源（difftest 连 ena 都比）</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="C23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_rf_we</t>
+          <t xml:space="preserve">disp*_dst_preg[6:0]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="0">
@@ -871,7 +871,7 @@
       </c>
       <c r="G23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 dst_vld；A6b：要与写回级同源（difftest 连 ena 都比）</t>
+          <t xml:space="preserve">内部有 ir_inst*_dst_preg（就是它从 RTU 拿到的号，6 位）</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_dst_preg[6:0]</t>
+          <t xml:space="preserve">disp*_old_preg[6:0]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="0">
@@ -908,7 +908,7 @@
       </c>
       <c r="G24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 ir_inst*_dst_preg（就是它从 RTU 拿到的号，6 位）</t>
+          <t xml:space="preserve">内部有 RAT 读口 rt_dp_inst*_rel_preg</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="C25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_old_preg[6:0]</t>
+          <t xml:space="preserve">disp*_src1_preg[6:0]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="0">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 RAT 读口 rt_dp_inst*_rel_preg</t>
+          <t xml:space="preserve">内部有 rt_dp_inst*_src1_data；**只有 CSR 指令有意义**</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="C26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_src1_preg[6:0]</t>
+          <t xml:space="preserve">disp*_csr_addr / _op / _imm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">12/3/5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="0">
@@ -982,7 +982,7 @@
       </c>
       <c r="G26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有 rt_dp_inst*_src1_data；**只有 CSR 指令有意义**</t>
+          <t xml:space="preserve">内部有（译码）；A6c：csr_op 要 **funct3 原样**（001/010/011 与 101/110/111）</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_csr_addr / _op / _imm</t>
+          <t xml:space="preserve">disp*_flags[6:0]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">12/3/5</t>
+          <t xml:space="preserve">3×7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="0">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部有（译码）；A6c：csr_op 要 **funct3 原样**（001/010/011 与 101/110/111）</t>
+          <t xml:space="preserve">内部散在 inst_type[4:0] / ir_decd；要按 RTU_FLG_* 打包{is_jalr,is_jal,is_mret,is_csr,intmask,is_store,is_branch}</t>
         </is>
       </c>
     </row>
@@ -1036,17 +1036,17 @@
       </c>
       <c r="C28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_flags[6:0]</t>
+          <t xml:space="preserve">disp*_sq_id[2:0]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×7</t>
+          <t xml:space="preserve">3×3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有）</t>
+          <t xml:space="preserve">—（缺，内部有类似的）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="0">
@@ -1056,34 +1056,34 @@
       </c>
       <c r="G28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">内部散在 inst_type[4:0] / ir_decd；要按 RTU_FLG_* 打包{is_jalr,is_jal,is_mret,is_csr,intmask,is_store,is_branch}</t>
+          <t xml:space="preserve">IDU 内部有 SDIQ 条目号，但那是**发射级**发给 LSU 的；RTU 要的是**派遣当拍**的槽号</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU→RTU</t>
+          <t xml:space="preserve">IDU 侧</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">disp*_sq_id[2:0]</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×3</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（缺，内部有类似的）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="0">
@@ -1093,56 +1093,56 @@
       </c>
       <c r="G29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 内部有 SDIQ 条目号，但那是**发射级**发给 LSU 的；RTU 要的是**派遣当拍**的槽号</t>
+          <t xml:space="preserve">A7：**一拍最多一条 CSR**（RTU 的 CSR 是单槽）；组内第二条要连同后面的指令截到下一拍</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">约束（非端口）</t>
+          <t xml:space="preserve">## IDU 顶层端口表变更（2026-10-08, commit cbcbd18 "idu chk"） —— 与 RTU 无关，但影响接线与冒烟台</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 侧</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">A7：**一拍最多一条 CSR**（RTU 的 CSR 是单槽）；组内第二条要连同后面的指令截到下一拍</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## IDU 顶层端口表变更（2026-10-08, commit cbcbd18 "idu chk"） —— 与 RTU 无关，但影响接线与冒烟台</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">IFU→IDU</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—（ifu2 不需要改）</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">ifu_idu_if_inst0/1/2_chk[24:0]</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3×25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">IDU **新增的输入口**。ifu2 侧本来就有这三根旁路输出（`rv32ifu2_top.v:204/207/210` 的 `idu_inst0/1/2_chk[24:0]`）⇒ 直接接。⚠️ 旧文档说"现核里 chk 只走了 0 路、ifu2 的 inst1/inst2_chk 在 mycpu.v:417/420 悬空"—— 接 C910 IDU 时这三根要全部接上</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IFU→IDU</t>
+          <t xml:space="preserve">IDU→IFU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（ifu2 不需要改）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="0">
@@ -1169,29 +1169,29 @@
       </c>
       <c r="E32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ifu_idu_if_inst0/1/2_chk[24:0]</t>
+          <t xml:space="preserve">idu_accept_num[1:0]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×25</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU **新增的输入口**。ifu2 侧本来就有这三根旁路输出（`rv32ifu2_top.v:204/207/210` 的 `idu_inst0/1/2_chk[24:0]`）⇒ 直接接。⚠️ 旧文档说"现核里 chk 只走了 0 路、ifu2 的 inst1/inst2_chk 在 mycpu.v:417/420 悬空"—— 接 C910 IDU 时这三根要全部接上</t>
+          <t xml:space="preserve">⚠️ **IDU 顶层把 `idu_ifu_inst0/1/2_ready` 三个输出删了，换成这一根**（同一次提交）。编码 `{inst2_ready|inst0_ready, inst2_ready}`（`ct_idu_top.sv:180`），取值只有 **{0,1,3}** —— 2 不可达（因为 `inst0_ready==inst1_ready` 恒相等，见 `ct_idu_id_ctrl.sv:36-38`）。语义 = **本拍从 IFU 收下几条（程序序前缀）**。✅ **ifu2 早就有这个口**（`rv32ifu2_top.v:212` "同拍消费的前缀条数"）⇒ 这次改动是**把 IDU 对齐到 ifu2**，不是新增负担</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU→IFU</t>
+          <t xml:space="preserve">IDU→(BIQ/BU)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="0">
@@ -1206,29 +1206,29 @@
       </c>
       <c r="E33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_accept_num[1:0]</t>
+          <t xml:space="preserve">idu_biq_chk[24:0]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">⚠️ **IDU 顶层把 `idu_ifu_inst0/1/2_ready` 三个输出删了，换成这一根**（同一次提交）。编码 `{inst2_ready|inst0_ready, inst2_ready}`（`ct_idu_top.sv:180`），取值只有 **{0,1,3}** —— 2 不可达（因为 `inst0_ready==inst1_ready` 恒相等，见 `ct_idu_id_ctrl.sv:36-38`）。语义 = **本拍从 IFU 收下几条（程序序前缀）**。✅ **ifu2 早就有这个口**（`rv32ifu2_top.v:212` "同拍消费的前缀条数"）⇒ 这次改动是**把 IDU 对齐到 ifu2**，不是新增负担</t>
+          <t xml:space="preserve">同一次提交新增的输出，把 chk 送到 BIQ（分支执行路径）。与 RTU 无关；记在这里是因为它是 `disp*_chk` 之外的第二个 chk 出口，别接混</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU→(BIQ/BU)</t>
+          <t xml:space="preserve">TB 侧</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="0">
@@ -1243,83 +1243,83 @@
       </c>
       <c r="E34" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_biq_chk[24:0]</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G34" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">同一次提交新增的输出，把 chk 送到 BIQ（分支执行路径）。与 RTU 无关；记在这里是因为它是 `disp*_chk` 之外的第二个 chk 出口，别接混</t>
+          <t xml:space="preserve">⚠️ **冒烟台已过时**：`tb/unit/tb_idu_c910.sv` 的端口连接是 `scripts/gen_idu_smoke_tb.py` 从 `ct_idu_top.sv` 端口表生成的，现在它还连着已删掉的 `idu_ifu_inst0/1/2_ready`，且缺 chk 三根 / `idu_accept_num` / `idu_biq_chk`。实测 `python3 scripts/gen_idu_smoke_tb.py --check` 报"需要重新生成" ⇒ **`make idu-unit` 现在会 elaborate 失败**，跑之前先重跑生成器</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">约束（非端口）</t>
+          <t xml:space="preserve">## 冲刷 与 映射恢复</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TB 侧</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">⚠️ **冒烟台已过时**：`tb/unit/tb_idu_c910.sv` 的端口连接是 `scripts/gen_idu_smoke_tb.py` 从 `ct_idu_top.sv` 端口表生成的，现在它还连着已删掉的 `idu_ifu_inst0/1/2_ready`，且缺 chk 三根 / `idu_accept_num` / `idu_biq_chk`。实测 `python3 scripts/gen_idu_smoke_tb.py --check` 报"需要重新生成" ⇒ **`make idu-unit` 现在会 elaborate 失败**，跑之前先重跑生成器</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 冲刷 与 映射恢复</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">RTU→IDU</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_ren_flush (+ rtu_backend_flush)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">rtu_yy_xx_flush</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">两边都是 T+1 那拍。⚠️ **别接 rtu_core_redirect**（T 拍，早一拍）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">暂无对应</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→IDU</t>
+          <t xml:space="preserve">RTU→(IDU)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_ren_flush (+ rtu_backend_flush)</t>
+          <t xml:space="preserve">rtu_ren_recover_vld</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="0">
@@ -1329,91 +1329,91 @@
       </c>
       <c r="E37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_yy_xx_flush</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">两边都是 T+1 那拍。⚠️ **别接 rtu_core_redirect**（T 拍，早一拍）</t>
+          <t xml:space="preserve">IDU 的写使能就是 flush 本身（同拍组合写 RAT），没有单独的 vld 口 ⇒ 可省</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→(IDU)</t>
+          <t xml:space="preserve">RTU→IDU</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_ren_recover_vld</t>
+          <t xml:space="preserve">rtu_ren_recover_map[223:0]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">224</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">rtu_idu_rt_recover_preg[191:0]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">192</t>
         </is>
       </c>
       <c r="G38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU 的写使能就是 flush 本身（同拍组合写 RAT），没有单独的 vld 口 ⇒ 可省</t>
+          <t xml:space="preserve">两边都是"32 个 lreg 的架构映射"，但**布局不同**（32×7 vs 32×6 每槽切位） ⇒ 适配层逐槽重排，不是切低位</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·需适配</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→IDU</t>
+          <t xml:space="preserve">IDU→RTU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_ren_recover_map[223:0]</t>
+          <t xml:space="preserve">preg_dealloc_mask[63:0]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">224</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_idu_rt_recover_preg[191:0]</t>
+          <t xml:space="preserve">idu_rtu_pst_preg_dealloc_mask[63:0]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">192</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="G39" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">两边都是"32 个 lreg 的架构映射"，但**布局不同**（32×7 vs 32×6 每槽切位） ⇒ 适配层逐槽重排，不是切低位</t>
+          <t xml:space="preserve">【改 RTU 侧：已于 2026-10-08 补口】⚠️ 极性：**位 = 1 表示这个号还被 store 引用着，不许回池**（名字里的 dealloc 读成"可以释放这些"正好反过来）。它是所有存活 SDIQ 表项的 src0 preg 的独热或（ct_idu_is_sdiq.sv:388-406）。**为什么必须接**：store 的"完成"不蕴含"数据已读"（lsu_st_da.sv:309）⇒ 更年轻的覆盖同一条 lreg 的指令退休时会把它还要读的号放回池子 ⇒ 重分配 ⇒ 静默错数。RTU 侧收下它是当**否决**用：释放先落第 5 态 RELEASE，掩码撤下才回 FREE。⚠️ 两个契约：① IDU 必须在冲刷那拍把它清零（不然号永久停在 RELEASE）；② 它只覆盖 SDIQ 的 src0（= store 数据），基址若在弹出后被重读则兜不住。⚠️ 交付的 IDU 里 SDIQ 表项的时钟 `src_mask_clk` 全仓无驱动 ⇒ 掩码恒 0，属"先决条件"（见下）。</t>
         </is>
       </c>
     </row>
@@ -1425,81 +1425,81 @@
       </c>
       <c r="B40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU→RTU</t>
+          <t xml:space="preserve">(适配层)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">preg_dealloc_mask[63:0]</t>
+          <t xml:space="preserve">复位极性</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">idu_rtu_pst_preg_dealloc_mask[63:0]</t>
+          <t xml:space="preserve">cpurst_b 低有效</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">【改 RTU 侧：已于 2026-10-08 补口】⚠️ 极性：**位 = 1 表示这个号还被 store 引用着，不许回池**（名字里的 dealloc 读成"可以释放这些"正好反过来）。它是所有存活 SDIQ 表项的 src0 preg 的独热或（ct_idu_is_sdiq.sv:388-406）。**为什么必须接**：store 的"完成"不蕴含"数据已读"（lsu_st_da.sv:309）⇒ 更年轻的覆盖同一条 lreg 的指令退休时会把它还要读的号放回池子 ⇒ 重分配 ⇒ 静默错数。RTU 侧收下它是当**否决**用：释放先落第 5 态 RELEASE，掩码撤下才回 FREE。⚠️ 两个契约：① IDU 必须在冲刷那拍把它清零（不然号永久停在 RELEASE）；② 它只覆盖 SDIQ 的 src0（= store 数据），基址若在弹出后被重读则兜不住。⚠️ 交付的 IDU 里 SDIQ 表项的时钟 `src_mask_clk` 全仓无驱动 ⇒ 掩码恒 0，属"先决条件"（见下）。</t>
+          <t xml:space="preserve">IDU 是 cpurst_b 低有效异步 / RTU 是 cpu_rst 高有效 ⇒ 适配层反相</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">## 先决条件（不是端口，但接之前必须先修）</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">(适配层)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">复位极性</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">cpurst_b 低有效</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">IDU 是 cpurst_b 低有效异步 / RTU 是 cpu_rst 高有效 ⇒ 适配层反相</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 先决条件（不是端口，但接之前必须先修）</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">IDU 内部</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">✅ **2026-10-08 已修，而且病因比原来记的多三条**。改名表要能用，**四处都得对**：① 表项时钟 `dep_clk`/`write_clk` 全仓无驱动（C910 工厂版的 gated clk cell 被剥掉了）；② `reg_write_en_arr[0:31]` **全文件没有任何赋值**（32 位总线算出来了没接过去）⇒ 写使能悬空 Z；③ 数组宽度错位：表项口是 `x_read_data[12:0]`/`x_create_data[10:0]`（C910 打包格式），wrapper 只声明成 **7 位** ⇒ 读侧截断、写侧错位。实测指纹：**给号 33 → 存进去变 8 → 读回来变 16**（每步错位 2 位）；④ `rt_reset_updt_preg`（x_l→p_l 复位映射）**零消费** ⇒ 上电后所有逻辑寄存器指向 p0。⚠️ **①②③ 已修并验证**（`make idu-unit` 的定向判据：某次派遣的 `old_preg` 必须变成 RTU 给的号）；**④ 还没修**，不修整核跑起来必错。详见 doc/DELIVERY_FIXES_2026-10-08.md</t>
         </is>
       </c>
     </row>
@@ -1535,43 +1535,6 @@
         </is>
       </c>
       <c r="G43" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">✅ **2026-10-08 已修，而且病因比原来记的多三条**。改名表要能用，**四处都得对**：① 表项时钟 `dep_clk`/`write_clk` 全仓无驱动（C910 工厂版的 gated clk cell 被剥掉了）；② `reg_write_en_arr[0:31]` **全文件没有任何赋值**（32 位总线算出来了没接过去）⇒ 写使能悬空 Z；③ 数组宽度错位：表项口是 `x_read_data[12:0]`/`x_create_data[10:0]`（C910 打包格式），wrapper 只声明成 **7 位** ⇒ 读侧截断、写侧错位。实测指纹：**给号 33 → 存进去变 8 → 读回来变 16**（每步错位 2 位）；④ `rt_reset_updt_preg`（x_l→p_l 复位映射）**零消费** ⇒ 上电后所有逻辑寄存器指向 p0。⚠️ **①②③ 已修并验证**（`make idu-unit` 的定向判据：某次派遣的 `old_preg` 必须变成 RTU 给的号）；**④ 还没修**，不修整核跑起来必错。详见 doc/DELIVERY_FIXES_2026-10-08.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">约束（非端口）</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">IDU 内部</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">⚠️ **2026-10-08 新发现，同一类毛病**：SDIQ 里 `ct_idu_is_sdiq.sv:38-39` 的 `src_mask_clk` / `cnt_clk` 也**全仓无驱动**（该文件只在 :139/:376/:394 把它们当 always 的时钟用）。后果有两个：① 上面那根 `preg_dealloc_mask` 的寄存器永不翻转 ⇒ 恒 0；② SDIQ 自己的表项计数器 `sdiq_entry_cnt` 也不动 ⇒ 它的满/空判据是死的。⇒ 接线前必须补上（与 RAT 时钟一起修）</t>
         </is>
@@ -2527,7 +2490,7 @@
       </c>
       <c r="C3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="0">
@@ -2549,7 +2512,7 @@
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="0">

--- a/doc/rtu_接口对照表.xlsx
+++ b/doc/rtu_接口对照表.xlsx
@@ -1713,7 +1713,7 @@
       </c>
       <c r="G5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">C910 的一热 preg 展开；我们是**按 iid 寻址**的（表项只存回绕位）⇒ 不用</t>
+          <t xml:space="preserve">⚠️ **2026-10-13 起不再是"暂无对应"** —— 见下面的写回门那一段。（原来记的理由"RTU 按 iid 寻址、不需要写哪个 preg"只对**完成**口成立；写回门要的正是"按 preg"的**寿命**信息，与 A9 那根掩码是同一类。）</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="G6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">同上：RTU 不需要"写哪个 preg"，它按 iid 找表项</t>
+          <t xml:space="preserve">同上：现在是写回门的一路源（`preg_wb_mask` 的 pipe3 项）</t>
         </is>
       </c>
     </row>
@@ -1762,81 +1762,81 @@
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LSU→RTU</t>
+          <t xml:space="preserve">各写口→RTU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">lsu_replay_vld / lsu_replay_iid[6:0]</t>
+          <t xml:space="preserve">preg_wb_mask[63:0]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1 / 7</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">lsu_rtu_wb_pipe4_flush  +  lsu_rtu_wb_pipe4_spec_fail</t>
+          <t xml:space="preserve">iu_idu_ex2_pipe{0,1,2}_wb_preg_{vld,expand} + lsu_rtu_wb_pipe3_wb_preg_{vld,expand} + (CSR rd 内部并)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1 + 1</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="G7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">store 投机写失败 ⇒ 要重放。**RTU 侧已加**（2026-10-08）：两个输入口 + ROB 表项的 `RTU_E_REPLAY` 位 + 第 5 类冲刷源 `RTU_FS_REPLAY`。适配层把 LSU 那两根**或**起来（对我们这条路径是同一个动作），iid 原样送。⚠️ 它跟完成**同拍**报 ⇒ RTU 里有一条同拍命中路径（否则那条 store 会在同一个边沿就退休、把内存写提交掉）</t>
+          <t xml:space="preserve">**写回门（2026-10-13 新增）**：位 = 1 ⇒ 这个号的生产者已经写回, 准回池。`RELEASE → FREE` 的第二道条件 (`rel_go_vec = rel_vec &amp; ~mask_ext &amp; wb_ok`)。让 LSU 那两根从"观察口"变成真信号；IU 三组在集成层或进来；**PRF 第 5 写口（CSR 的 rd, 由 RTU 自己在退休拍写）没有广播, 由 `RTU.v` 内部补** —— 漏了它 CSR 指令的号会永久出池。端口契约见 rtu_plan_zh.md §6.1 的 A10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 访存异常（LSU → RTU）—— 2026-10-08 新增；2026-10-10 改成三路平行</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">LSU→RTU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">lsu_replay_vld / lsu_replay_iid[6:0]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1 / 7</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">lsu_rtu_wb_pipe4_flush  +  lsu_rtu_wb_pipe4_spec_fail</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1 + 1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">store 投机写失败 ⇒ 要重放。**RTU 侧已加**（2026-10-08）：两个输入口 + ROB 表项的 `RTU_E_REPLAY` 位 + 第 5 类冲刷源 `RTU_FS_REPLAY`。适配层把 LSU 那两根**或**起来（对我们这条路径是同一个动作），iid 原样送。⚠️ 它跟完成**同拍**报 ⇒ RTU 里有一条同拍命中路径（否则那条 store 会在同一个边沿就退休、把内存写提交掉）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·需适配</t>
+          <t xml:space="preserve">## 访存异常（LSU → RTU）—— 2026-10-08 新增；2026-10-10 改成三路平行</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LSU→RTU</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">expt_ld_vld / expt_ld_iid[6:0] / expt_ld_cause[4:0] / expt_ld_tval[31:0]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">1 / 7 / 5 / 32</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">lsu_rtu_wb_pipe3_expt_vld / _expt_addr[31:0]</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">1 / 32</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">**load 侧异常**（新加的两根）。语义 = **地址非对齐**：`ld_ag_expt = !ld_ag_align`（`lsu_ld_ag.sv:286-297`，按 `{inst_size, addr[2:0]}` 判：BYTE 任意 / HALF 需 `addr[0]=0` / WORD 需 `addr[1:0]=00`），随流水 AG→DC→DA→WB 打到底，**与 `lsu_rtu_wb_pipe3_cmplt` 同拍、同 iid**。⇒ 映射：`expt_ld_iid` = 同拍 `lsu_rtu_wb_pipe3_iid`（**原样，不许重编码**）；`expt_ld_cause` = **5'd4**（`EXC_LOAD_MISALIGNED`，defines.vh:301）；`expt_ld_tval` = `_expt_addr`（= `ld_da_addr`）</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">expt_st_vld / expt_st_iid[6:0] / expt_st_cause[4:0] / expt_st_tval[31:0]</t>
+          <t xml:space="preserve">expt_ld_vld / expt_ld_iid[6:0] / expt_ld_cause[4:0] / expt_ld_tval[31:0]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="0">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">lsu_rtu_wb_pipe4_expt_vld / _expt_addr[31:0]</t>
+          <t xml:space="preserve">lsu_rtu_wb_pipe3_expt_vld / _expt_addr[31:0]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="0">
@@ -1873,44 +1873,44 @@
       </c>
       <c r="G10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">**store 侧异常**（同上）。`st_ag_expt = !st_ag_align`（`lsu_st_ag.sv:142-153`）。⇒ 映射：`expt_st_iid` 取同拍 `lsu_rtu_wb_pipe4_iid`；`expt_st_cause` = **5'd6**（`EXC_STORE_MISALIGNED`，defines.vh:303）；`expt_st_tval` = `_expt_addr`（= `st_da_addr0`）</t>
+          <t xml:space="preserve">**load 侧异常**（新加的两根）。语义 = **地址非对齐**：`ld_ag_expt = !ld_ag_align`（`lsu_ld_ag.sv:286-297`，按 `{inst_size, addr[2:0]}` 判：BYTE 任意 / HALF 需 `addr[0]=0` / WORD 需 `addr[1:0]=00`），随流水 AG→DC→DA→WB 打到底，**与 `lsu_rtu_wb_pipe3_cmplt` 同拍、同 iid**。⇒ 映射：`expt_ld_iid` = 同拍 `lsu_rtu_wb_pipe3_iid`（**原样，不许重编码**）；`expt_ld_cause` = **5'd4**（`EXC_LOAD_MISALIGNED`，defines.vh:301）；`expt_ld_tval` = `_expt_addr`（= `ld_da_addr`）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">约束（非端口）</t>
+          <t xml:space="preserve">已有·需适配</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">适配层</t>
+          <t xml:space="preserve">LSU→RTU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">expt_st_vld / expt_st_iid[6:0] / expt_st_cause[4:0] / expt_st_tval[31:0]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 / 7 / 5 / 32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">lsu_rtu_wb_pipe4_expt_vld / _expt_addr[31:0]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 / 32</t>
         </is>
       </c>
       <c r="G11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">✅ **2026-10-10 已落地：适配层不再仲裁，三路平行送进 RTU**。原来的做法是「两源取最旧 + 再与其它源取最旧」，两个 `RTU_iid_cmp` 都在适配层 —— **那是个补不回来的窟窿**：load 与 store 是两条独立流水、可以同拍都报，上游只能送一条；若送的是年轻那条，年长那条的异常信息当场丢失、且**以后不会再报**（它已离开流水），而它比 trap 那条老 ⇒ **不在冲刷范围内** ⇒ 带着「无异常」的表项正常退休，异常**永久丢失**。RTU 内部那级（保持项「更老才覆盖」）只救得了**跨拍**冲突。⇒ 现在 RTU 的异常口是**三路**（`expt_iu_*` / `expt_ld_*` / `expt_st_*`），与 C910 的 `iu_rtu_pipe0 / pipe3 / pipe4_expt_*` 一一对应，锦标赛在 `RTU_expt` 里做（`cmp(iu,ld) → w1`、`cmp(w1,st) → w2`、`cmp(w2,held) → take`）。适配层只留「完成门控 + cause 编码」两件跨界必需的事。⚠️ 这正是本表原来写的「另一条路」（那时说的是加宽到 2 路），2026-10-10 按 3 路做了</t>
+          <t xml:space="preserve">**store 侧异常**（同上）。`st_ag_expt = !st_ag_align`（`lsu_st_ag.sv:142-153`）。⇒ 映射：`expt_st_iid` 取同拍 `lsu_rtu_wb_pipe4_iid`；`expt_st_cause` = **5'd6**（`EXC_STORE_MISALIGNED`，defines.vh:303）；`expt_st_tval` = `_expt_addr`（= `st_da_addr0`）</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LSU 侧</t>
+          <t xml:space="preserve">适配层</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">✅ **报异常时 LSU 会压掉访存**，口径自洽、不用 RTU 兜底：`st_da_rb_create_vld_unmask ... &amp;&amp; !st_da_expt`（不发总线写，`lsu_st_da.sv:293`）、`st_da_idu_secd_vld ... &amp;&amp; !st_da_expt`（不发第二拍，:332）、`ld_da_data_vld ... &amp;&amp; !ld_da_expt`（不写回，`lsu_ld_da.sv:521`）。配上 RTU 侧 `RTU_commit.v:294` 的 `commit_vld` 已经 `&amp; ~trap_hit`（陷阱那条**不发提交广播**）⇒ 非对齐 store **不会落内存**。两头正好对上</t>
+          <t xml:space="preserve">✅ **2026-10-10 已落地：适配层不再仲裁，三路平行送进 RTU**。原来的做法是「两源取最旧 + 再与其它源取最旧」，两个 `RTU_iid_cmp` 都在适配层 —— **那是个补不回来的窟窿**：load 与 store 是两条独立流水、可以同拍都报，上游只能送一条；若送的是年轻那条，年长那条的异常信息当场丢失、且**以后不会再报**（它已离开流水），而它比 trap 那条老 ⇒ **不在冲刷范围内** ⇒ 带着「无异常」的表项正常退休，异常**永久丢失**。RTU 内部那级（保持项「更老才覆盖」）只救得了**跨拍**冲突。⇒ 现在 RTU 的异常口是**三路**（`expt_iu_*` / `expt_ld_*` / `expt_st_*`），与 C910 的 `iu_rtu_pipe0 / pipe3 / pipe4_expt_*` 一一对应，锦标赛在 `RTU_expt` 里做（`cmp(iu,ld) → w1`、`cmp(w1,st) → w2`、`cmp(w2,held) → take`）。适配层只留「完成门控 + cause 编码」两件跨界必需的事。⚠️ 这正是本表原来写的「另一条路」（那时说的是加宽到 2 路），2026-10-10 按 3 路做了</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">适配层</t>
+          <t xml:space="preserve">LSU 侧</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="0">
@@ -1984,19 +1984,19 @@
       </c>
       <c r="G13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">🔴 **`expt_vld` 必须与同口的 `cmplt` 相与之后再送进 RTU**（iid/tval 也按那一拍取）。这不是保险，是必须 —— 两根的相位现在**不保证一致**：`lsu_ld_wb.sv:165-175` 那段新加的 `always` **缺 begin/end**，于是 `ld_wb_expt` / `ld_wb_expt_addr` 变成 `ld_wb_pre_expt_vld` / `ld_da_wb_expt_addr` 的**无条件一拍延迟**（只在 `if (!cpurst_b)` 和 `else if (ld_wb_pre_inst_vld)` 各自的第一句上有条件），而导出的 cmplt `lsu_rtu_wb_pipe3_cmplt = ld_wb_inst_vld` 是**有门控**的（:152-162，置位要 `ld_wb_pre_inst_vld`、冲刷那拍清零）⇒ **会出现 expt_vld=1 而 cmplt=0 的拍**，而那一拍的 `lsu_rtu_wb_pipe3_iid` 是**残留值**。真会碰上的两种情形：① 冲刷那拍（cmplt 被清、expt 不被清）；② `ld_da_wb_cmplt_req = ld_da_inst_vld &amp;&amp; !ld_da_secd`（`lsu_ld_da.sv:515`）而 `ld_da_wb_expt_vld = ld_da_expt`（:516）是**裸**的 —— `ld_da_expt` 只在复位与 `ld_dc_da_inst_vld` 时更新（:268/:292），**没有冲刷清零**，`ld_da_inst_vld` 却有 ⇒ 两者脱节。⚠️ 后果是**静默**的（不报 x/z）：拿裸 expt_vld 去报，会按错误 iid 报异常，RTU 收进单表项一直挂到那条 iid 退休 ⇒ 冤枉一条无辜指令陷入、或静默掐掉它的退休；只有 difftest 能抓。⇒ 建议同时请同事补上那段 begin/end —— **store 侧 `lsu_st_wb.sv:59-74` 写法是对的**（begin/end + 用 `st_wb_pre_inst_vld` 门控），照着改即可</t>
+          <t xml:space="preserve">✅ **报异常时 LSU 会压掉访存**，口径自洽、不用 RTU 兜底：`st_da_rb_create_vld_unmask ... &amp;&amp; !st_da_expt`（不发总线写，`lsu_st_da.sv:293`）、`st_da_idu_secd_vld ... &amp;&amp; !st_da_expt`（不发第二拍，:332）、`ld_da_data_vld ... &amp;&amp; !ld_da_expt`（不写回，`lsu_ld_da.sv:521`）。配上 RTU 侧 `RTU_commit.v:294` 的 `commit_vld` 已经 `&amp; ~trap_hit`（陷阱那条**不发提交广播**）⇒ 非对齐 store **不会落内存**。两头正好对上</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LSU→(RTU)</t>
+          <t xml:space="preserve">适配层</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="0">
@@ -2011,29 +2011,29 @@
       </c>
       <c r="E14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">lsu_rtu_async_expt_vld / _addr[31:0]</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1 / 32</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">⚠️ **这两根现在只是 `lsu_top` 的内部信号**（`lsu_top.sv:685-686`），**没引到顶层** ⇒ RTU 拿不到"总线错误"这类异常。源在 `lsu_ld_wb.sv:264`（`ld_wb_data_vld &amp;&amp; ld_wb_bus_err`）。要不要引出来由 RTU↔LSU 定；现在归"暂无对应"，接线时要**显式确认**是"不需要"还是"漏了"</t>
+          <t xml:space="preserve">🔴 **`expt_vld` 必须与同口的 `cmplt` 相与之后再送进 RTU**（iid/tval 也按那一拍取）。这不是保险，是必须 —— 两根的相位现在**不保证一致**：`lsu_ld_wb.sv:165-175` 那段新加的 `always` **缺 begin/end**，于是 `ld_wb_expt` / `ld_wb_expt_addr` 变成 `ld_wb_pre_expt_vld` / `ld_da_wb_expt_addr` 的**无条件一拍延迟**（只在 `if (!cpurst_b)` 和 `else if (ld_wb_pre_inst_vld)` 各自的第一句上有条件），而导出的 cmplt `lsu_rtu_wb_pipe3_cmplt = ld_wb_inst_vld` 是**有门控**的（:152-162，置位要 `ld_wb_pre_inst_vld`、冲刷那拍清零）⇒ **会出现 expt_vld=1 而 cmplt=0 的拍**，而那一拍的 `lsu_rtu_wb_pipe3_iid` 是**残留值**。真会碰上的两种情形：① 冲刷那拍（cmplt 被清、expt 不被清）；② `ld_da_wb_cmplt_req = ld_da_inst_vld &amp;&amp; !ld_da_secd`（`lsu_ld_da.sv:515`）而 `ld_da_wb_expt_vld = ld_da_expt`（:516）是**裸**的 —— `ld_da_expt` 只在复位与 `ld_dc_da_inst_vld` 时更新（:268/:292），**没有冲刷清零**，`ld_da_inst_vld` 却有 ⇒ 两者脱节。⚠️ 后果是**静默**的（不报 x/z）：拿裸 expt_vld 去报，会按错误 iid 报异常，RTU 收进单表项一直挂到那条 iid 退休 ⇒ 冤枉一条无辜指令陷入、或静默掐掉它的退休；只有 difftest 能抓。⇒ 建议同时请同事补上那段 begin/end —— **store 侧 `lsu_st_wb.sv:59-74` 写法是对的**（begin/end + 用 `st_wb_pre_inst_vld` 门控），照着改即可</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">约束（非端口）</t>
+          <t xml:space="preserve">暂无对应</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IDU+LSU 口径</t>
+          <t xml:space="preserve">LSU→(RTU)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="0">
@@ -2048,66 +2048,66 @@
       </c>
       <c r="E15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">lsu_rtu_async_expt_vld / _addr[31:0]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1 / 32</t>
         </is>
       </c>
       <c r="G15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">❓ **非对齐到底走 trap 还是走硬件拆分**，两边还都留着通路：LSU 一边报 `expt` 并压掉访存，一边仍保留 `idu_lsu_{ld,st}_unalign_2nd` → `ld_ag_secd` / `st_ag_secd` 的**拆两次访存**机制（`lsu_ld_ag.sv:219`、`lsu_st_ag.sv`）。两者不能并存：**走 trap ⇒ IDU 不该再发 `unalign_2nd`；走拆分 ⇒ 就不该报 `expt`**。接 RTU 之前要跟 IDU/LSU 两位定死（RTU 只按"收到 expt 就用 cause 4/6 陷入"设计）</t>
+          <t xml:space="preserve">⚠️ **这两根现在只是 `lsu_top` 的内部信号**（`lsu_top.sv:685-686`），**没引到顶层** ⇒ RTU 拿不到"总线错误"这类异常。源在 `lsu_ld_wb.sv:264`（`ld_wb_data_vld &amp;&amp; ld_wb_bus_err`）。要不要引出来由 RTU↔LSU 定；现在归"暂无对应"，接线时要**显式确认**是"不需要"还是"漏了"</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 提交 / 冲刷（RTU → LSU）</t>
+          <t xml:space="preserve">约束（非端口）</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">IDU+LSU 口径</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">❓ **非对齐到底走 trap 还是走硬件拆分**，两边还都留着通路：LSU 一边报 `expt` 并压掉访存，一边仍保留 `idu_lsu_{ld,st}_unalign_2nd` → `ld_ag_secd` / `st_ag_secd` 的**拆两次访存**机制（`lsu_ld_ag.sv:219`、`lsu_st_ag.sv`）。两者不能并存：**走 trap ⇒ IDU 不该再发 `unalign_2nd`；走拆分 ⇒ 就不该报 `expt`**。接 RTU 之前要跟 IDU/LSU 两位定死（RTU 只按"收到 expt 就用 cause 4/6 陷入"设计）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">已有·直接接</t>
+          <t xml:space="preserve">## 提交 / 冲刷（RTU → LSU）</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→LSU</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">rtu_backend_flush</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">rtu_yy_xx_flush</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">都是 T+1 单拍脉冲</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2124,27 +2124,27 @@
       </c>
       <c r="C18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_yy_xx_commit0/1/2  +  _iid</t>
+          <t xml:space="preserve">rtu_backend_flush</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3 + 21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_yy_xx_commit0/1/2  +  _iid</t>
+          <t xml:space="preserve">rtu_yy_xx_flush</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3 + 21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">**RTU 侧已加**（2026-10-08，照 C910 `ct_rtu_rob_rt.v:2723-2731`）：退休窗口 3 条 iid 广播 + **真的提交了**的脉冲（陷阱那条不发、被中断 squash 的不发）。两边都是寄存器输出、**成对锁存** —— 消费方必须同一个边沿成对采样</t>
+          <t xml:space="preserve">都是 T+1 单拍脉冲</t>
         </is>
       </c>
     </row>
@@ -2161,64 +2161,64 @@
       </c>
       <c r="C19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_lsu_async_flush</t>
+          <t xml:space="preserve">rtu_yy_xx_commit0/1/2  +  _iid</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3 + 21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_lsu_async_flush</t>
+          <t xml:space="preserve">rtu_yy_xx_commit0/1/2  +  _iid</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3 + 21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">**RTU 侧已加**（2026-10-08），当前**恒 0**：C910 里它是**调试请求**的异步冲刷（`ct_rtu_retire.v:2005` 的 `async_flush = dbgreq_ack_jdbreq`），本核没有 debug 模块。LSU 拿它清 WMB/SQ（lsu_sq.sv:527、lsu_wmb_ce.sv:62）；将来接 debug 时接到这里即可</t>
+          <t xml:space="preserve">**RTU 侧已加**（2026-10-08，照 C910 `ct_rtu_rob_rt.v:2723-2731`）：退休窗口 3 条 iid 广播 + **真的提交了**的脉冲（陷阱那条不发、被中断 squash 的不发）。两边都是寄存器输出、**成对锁存** —— 消费方必须同一个边沿成对采样</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">暂无对应</t>
+          <t xml:space="preserve">已有·直接接</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→(LSU)</t>
+          <t xml:space="preserve">RTU→LSU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_store_vld0/1/2</t>
+          <t xml:space="preserve">rtu_lsu_async_flush</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">rtu_lsu_async_flush</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">我们 RTU §6.2 的 store 提交口；LSU 侧没有对应输入 ⇒ 若走"iid 广播"那套就不需要它</t>
+          <t xml:space="preserve">**RTU 侧已加**（2026-10-08），当前**恒 0**：C910 里它是**调试请求**的异步冲刷（`ct_rtu_retire.v:2005` 的 `async_flush = dbgreq_ack_jdbreq`），本核没有 debug 模块。LSU 拿它清 WMB/SQ（lsu_sq.sv:527、lsu_wmb_ce.sv:62）；将来接 debug 时接到这里即可</t>
         </is>
       </c>
     </row>
@@ -2235,12 +2235,12 @@
       </c>
       <c r="C21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">rtu_store_sq_id0/1/2[2:0]</t>
+          <t xml:space="preserve">rtu_store_vld0/1/2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×3</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="0">
@@ -2255,34 +2255,34 @@
       </c>
       <c r="G21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">同上</t>
+          <t xml:space="preserve">我们 RTU §6.2 的 store 提交口；LSU 侧没有对应输入 ⇒ 若走"iid 广播"那套就不需要它</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">需新增</t>
+          <t xml:space="preserve">暂无对应</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LSU→RTU</t>
+          <t xml:space="preserve">RTU→(LSU)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">sq_rdy0/1/2  (RTU 已声明)</t>
+          <t xml:space="preserve">rtu_store_sq_id0/1/2[2:0]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3×1</t>
+          <t xml:space="preserve">3×3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—（LSU 侧要产生）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="0">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="G22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">【改 LSU 侧：产生这三根】RTU §6.1 已有这三个输入（"这条 store 的数据就绪了吗"），现在 mycpu.v 恒接 1</t>
+          <t xml:space="preserve">同上</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">sq_stall  (RTU 已声明)</t>
+          <t xml:space="preserve">sq_rdy0/1/2  (RTU 已声明)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3×1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="0">
@@ -2329,56 +2329,56 @@
       </c>
       <c r="G23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">【改 LSU 侧：产生这一根】存储队列满/下游忙 ⇒ 压退休宽度；现在恒接 0</t>
+          <t xml:space="preserve">【改 LSU 侧：产生这三根】RTU §6.1 已有这三个输入（"这条 store 的数据就绪了吗"），现在 mycpu.v 恒接 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">## 约束（不是线，但接之前要知道）</t>
+          <t xml:space="preserve">需新增</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">LSU→RTU</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">sq_stall  (RTU 已声明)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—（LSU 侧要产生）</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">【改 LSU 侧：产生这一根】存储队列满/下游忙 ⇒ 压退休宽度；现在恒接 0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">约束（非端口）</t>
+          <t xml:space="preserve">## 约束（不是线，但接之前要知道）</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RTU→LSU</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">(rtu_yy_xx_commit*_iid)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">(LSU 内部表项里存的 iid)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">⚠️ 广播出去的 iid 必须与 LSU 表项里存的**是同一个号**（那个号追到源头就是 RTU 在派遣那拍发的 `rtu_disp_iid*`）⇒ **不许在适配层重编码、也不许偏一拍**，否则"段不匹配"的后果是静默的：store 永远等不到提交、或提前提交</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2390,30 +2390,67 @@
       </c>
       <c r="B26" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">RTU→LSU</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">(rtu_yy_xx_commit*_iid)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">(LSU 内部表项里存的 iid)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">⚠️ 广播出去的 iid 必须与 LSU 表项里存的**是同一个号**（那个号追到源头就是 RTU 在派遣那拍发的 `rtu_disp_iid*`）⇒ **不许在适配层重编码、也不许偏一拍**，否则"段不匹配"的后果是静默的：store 永远等不到提交、或提前提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">约束（非端口）</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">IDU+LSU 队列深度</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr" s="0">
+      <c r="C27" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">disp*_sq_id[2:0]</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr" s="0">
+      <c r="D27" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr" s="0">
+      <c r="E27" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">SQ_ENTRY=6 / SDIQ_ENTRY=4 / LSIQ_ENTRY=8</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr" s="0">
+      <c r="F27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">2026-10-08 核过的实际档位（`lsu_top.sv:3-5`）：`SQ_ENTRY = 6` ⇒ 槽号 0..5 正好 3 位，**与 RTU 的 `disp*_sq_id[2:0]` 严丝合缝**；`SDIQ_ENTRY = 4`（对 IDU 的 `idu_lsu_st_sdiq_entry[3:0]`）；`LSIQ_ENTRY = 8`（对 IDU 的 `idu_lsu_ld/st_lch_entry[7:0]`）。⚠️ **旧文档正文里写的 `LSIQ_ENTRY = 12` 已过期** —— 2026-10-08 的 commit 165dfd5 "位宽对齐 64 preg / 8 LSIQ" 已把它改成 8。RTU 只用 `sq_id`，与 LSIQ 深度无关</t>
         </is>
@@ -2517,7 +2554,7 @@
       </c>
       <c r="D4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>

--- a/doc/rtu_接口对照表.xlsx
+++ b/doc/rtu_接口对照表.xlsx
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SQ_ENTRY=6 / SDIQ_ENTRY=4 / LSIQ_ENTRY=8</t>
+          <t xml:space="preserve">SQ_ENTRY=6 / SDIQ_ENTRY=4 / LSIQ_ENTRY=12</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="0">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2026-10-08 核过的实际档位（`lsu_top.sv:3-5`）：`SQ_ENTRY = 6` ⇒ 槽号 0..5 正好 3 位，**与 RTU 的 `disp*_sq_id[2:0]` 严丝合缝**；`SDIQ_ENTRY = 4`（对 IDU 的 `idu_lsu_st_sdiq_entry[3:0]`）；`LSIQ_ENTRY = 8`（对 IDU 的 `idu_lsu_ld/st_lch_entry[7:0]`）。⚠️ **旧文档正文里写的 `LSIQ_ENTRY = 12` 已过期** —— 2026-10-08 的 commit 165dfd5 "位宽对齐 64 preg / 8 LSIQ" 已把它改成 8。RTU 只用 `sq_id`，与 LSIQ 深度无关</t>
+          <t xml:space="preserve">`SQ_ENTRY = 6` ⇒ 槽号 0..5 正好 3 位，**与 RTU 的 `disp*_sq_id[2:0]` 严丝合缝**；`SDIQ_ENTRY = 4`（对 IDU 的 `idu_lsu_st_sdiq_entry[3:0]`）。⚠️ **`LSIQ_ENTRY` 的历史是 12 → 8 → 12**：2026-10-08 的 commit 165dfd5 "位宽对齐 64 preg / 8 LSIQ" 曾把它砍到 8；2026-10-16 按 C910 原版深度放回 **12**（`mySoC/lsiq_defines.vh` 是真源，IDU 的 `idu_lsu_ld/st_lch_entry` 现在是 `[11:0]`）。RTU 只用 `sq_id`，与 LSIQ 深度无关 —— 这条留着是提醒别再照抄旧数</t>
         </is>
       </c>
     </row>
